--- a/Excel/9_Refrigerants_WIP_v02.xlsx
+++ b/Excel/9_Refrigerants_WIP_v02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067F1546-E2F1-405D-8E0B-8CFB6744C995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C5149A-74FE-4741-BC1B-71811552786A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="37170" windowHeight="19920" activeTab="3" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1815" yWindow="825" windowWidth="36060" windowHeight="19710" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -19793,17 +19793,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADQALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAxACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzACAAaQBuAGMAbAB1AGQAaQBuAGcAIABsAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgACAAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA1AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAIAAoAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwAKQBcACIALAAgAFwAIgBGAHUAZQBsACAAdQBuAGkAdABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAE8AMgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAEgANABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABOADIATwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAG8AbQBiAGkAbgBlAGQAIABnAGEAcwBlAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAyACwAIAAwAC4AMAAzACwAIAA1ADEALgA2ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAbQBpAG4AZQAgAHcAYQBzAHQAZQAgAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4AOQAsACAANAAuADYALAAgADAALgAzACwAIAA1ADYALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAoAHIAZQB2AGUAcgB0AGkAbgBnACAAdABvACAAcwB0AGEAbgBkAGEAcgBkACAAYwBvAG4AZABpAHQAaQBvAG4AcwApAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVQBuAHAAcgBvAGMAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAA2ADIAOQAsACAAXAAiAG0AMwBcACIALAAgADUANgAuADUALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANgAuADUANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBrAGUAIABvAHYAZQBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAxADgAMQAsACAAXAAiAG0AMwBcACIALAAgADMANwAuADAALAAgADAALgAwADMALAAgADAALgAwADUALAAgADMANwAuADAAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABhAHMAdAAgAGYAdQByAG4AYQBjAGUAIABnAGEAcwBcACIALAAgADAALgAwADAANAAwACwAIABcACIAbQAzAFwAIgAsACAAMgAzADQALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAAyACwAIAAyADMANAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADAANAAsACAAMAAuADAAMwAsACAANgAwAC4AMgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBMAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAGUAbwB1AHMAIABmAG8AcwBzAGkAbAAgAGYAdQBlAGwAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA5ADAALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABhAG4AZABmAGkAbABsACAAYgBpAG8AZwBhAHMAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtAGUAdABoAGEAbgBlACAAbwBuAGwAeQApAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAsACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAwAC4AMAAzADcAMAAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAG0AZQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAAMAAuADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAeQBkAHIAbwBnAGUAbgBcACIALAAgADAALgAwADEAMgAyACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADAALgAwACwAIAAwAC4ANQAsACAAMAAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIAAxACwAIABcACIARwBKAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIAB3AGUAcgBlACAAYQBkAGQAZQBkACwAIABlAGEAYwBoACAAdwBpAHQAaAAgAGEAbgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAMQAgAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwALgAgAFQAaABpAHMAIABpAHMAIABmAG8AcgAgAHUAcwBlAHIAcwAgAHcAaABvACAAaABhAHYAZQAgAGYAdQBlAGwAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABkAGEAdABhACAAaQBuACAARwBKACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbQAzAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA2AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAdABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE0AZQB0AHIAbwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAATgBhAHQAdQByAGEAbAAgAEcAYQBzACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgBvAG4AIAAtACAATQBlAHQAcgBvAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgADQALgAwACwAIAA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIAA4AC4AOAAsACAANwAuADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADEAMAAuADcALAAgADEAMAAuADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAA0AC4AMQAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgADQALgAxACwAIAA0AC4AMABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAE4AUwBXACAAYQBuAGQAIABBAEMAVAAgAHMAcABsAGkAdAAgAGkAbgB0AG8AIABzAGUAcABhAHIAYQB0AGUAIAByAG8AdwBzAC4AIABcAHUAMAAwADIANwBDAFwAdQAwADAAMgA3ACAAVgBhAGwAdQBlAHMAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAGEAbgBkACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAdABoAG8AcwBlACAAZgBvAHIAIABWAGkAYwB0AG8AcgBpAGEAIABhAG4AZAAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAHIAZQBzAHAAZQBjAHQAaQB2AGUAbAB5AC4AIAAoAFMAZQBlACAAYQBwAHAAZQBuAGQAaQBjAGUAcwApAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEEAcwAgAFMAYwBvAHAAZQAgADMAIABmAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAYQB0ACAAdABoAGUAIABwAG8AaQBuAHQAIAB3AGgAZQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABpAHMAIABkAGUAbABpAHYAZQByAGUAZAAgAHQAbwAgAGUAbgBkACAAdQBzAGUAcgBzACwAIABpAHQAIABpAHMAIABuAGUAYwBlAHMAcwBhAHIAeQAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAYQB0ACAAZQBhAGMAaAAgAG8AZgAgAHQAaABlACAAbABvAGEAZAAgAGMAZQBuAHQAcgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBHAGEAcwAgAHIAZQBhAGMAaABlAHMAIABlAG4AZAAgAHUAcwBlAHIAcwAgAGUAaQB0AGgAZQByACAAZgByAG8AbQAgAHQAaABlACAAbQBlAHQAcgBvACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABuAGUAdAB3AG8AcgBrAHMAIABvAHIAIABkAGkAcgBlAGMAdAAgAGYAcgBvAG0AIAB0AGgAZQAgAGgAaQBnAGgAIAAtACAAcAByAGUAcwBzAHUAcgBlACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABwAGkAcABlAGwAaQBuAGUAcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAEgAbwB1AHMAZQBoAG8AbABkAHMAIABhAG4AZAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB1AHMAZQByAHMAIAB0AGUAbgBkACAAdABvACAAYgBlACAAcwBlAHIAdgBlAGQAIABiAHkAIAB0AGgAZQAgAGYAbwByAG0AZQByACwAIABhAG4AZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAGcAZQBuAGUAcgBhAHQAbwByAHMAIABhAG4AZAAgAGwAYQByAGcAZQAgAGkAbgBkAHUAcwB0AHIAaQBhAGwAIABwAGwAYQBuAHQAcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGwAYQB0AHQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBNAGUAdAByAG8AIABpAHMAIABkAGUAZgBpAG4AZQBkACAAYQBzACAAbABvAGMAYQB0AGUAZAAgAG8AbgAgAG8AcgAgAGUAYQBzAHQAIABvAGYAIAB0AGgAZQAgAGQAaQB2AGkAZABpAG4AZwAgAHIAYQBuAGcAZQAgAGkAbgAgAE4AUwBXACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAEMAYQBuAGIAZQByAHIAYQAgAGEAbgBkACAAUQB1AGUAYQBuAGIAZQB5AGEAbgAsACAATQBlAGwAYgBvAHUAcgBuAGUALAAgAEIAcgBpAHMAYgBhAG4AZQAsACAAQQBkAGUAbABhAGkAZABlACAAbwByACAAUABlAHIAdABoAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIATwB0AGgAZQByAHcAaQBzAGUALAAgAHQAaABlACAAbgBvAG4AIAAtACAAbQBlAHQAcgBvACAAZgBhAGMAdABvAHIAIABzAGgAbwB1AGwAZAAgAGIAZQAgAHUAcwBlAGQALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEYAYQBjAHQAbwByAHMAIABhAHIAZQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAGEAbABsACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAHcAaABpAGMAaAAgAG0AYQB5ACAAaQBuAGMAbAB1AGQAZQAgAGMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIAVABhAGIAbABlACAANgAgAGkAcwAgAG4AbwB0ACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHQAbwAgAGUAdABoAGEAbgBlAC4AIABTAGUAZQAgAFQAYQBiAGwAZQAgADcAIABJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEMAIAA9ACAAQwBvAG4AZgBpAGQAZQBuAHQAaQBhAGwALgAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAHQAaABlACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIABhAHIAZQAgAG4AbwB0ACAAYQB2AGEAaQBsAGEAYgBsAGUAIABkAHUAZQAgAHQAbwAgAGMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAGkAdAB5ACAAYwBvAG4AcwB0AHIAYQBpAG4AdABzACAAdABoAGEAdAAgAGEAcgBpAHMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAGEAIABsAGkAbQBpAHQAZQBkACAAbgB1AG0AYgBlAHIAIABvAGYAIABOAEcARQBSACAAZABhAHQAYQAgAGkAbgBwAHUAdABzAC4AIABJAHQAIABpAHMAIABzAHUAZwBnAGUAcwB0AGUAZAAgAHQAaABhAHQAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAHQAaABlACAAdQBzAGUAIABvAGYAIAB0AGgAZQAgAFYAaQBjAHQAbwByAGkAYQBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGkAcwAgAGEAcABwAHIAbwBwAHIAaQBhAHQAZQAsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAHcAaABpAGwAZQAgAGYAbwByACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZABvACAAbgBvAHQAIABpAG4AYwBsAHUAZABlACAAZgB1AGcAaQB0AGkAdgBlACAAZQBtAGkAcwBzAGkAbwBuACAAbABlAGEAawBhAGcAZQAgAGYAcgBvAG0AIABsAG8AdwAgAHAAcgBlAHMAcwB1AHIAZQAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlACAAbgBlAHQAdwBvAHIAawBzACAAdwBoAGkAbABlACAAdABoAG8AcwBlACAAZgByAG8AbQAgAGgAaQBnAGgAIABwAHIAZQBzAHMAdQByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZwBhAHMAIABuAGUAdAB3AG8AcgBrAHMAIABhAHIAZQAgAGMAbwBuAHMAaQBkAGUAcgBlAGQAIABuAGUAZwBsAGkAZwBpAGIAbABlAC4AXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMALAAgAGkAbgBjAGwAdQBkAGkAbgBnACAAYwBlAHIAdABhAGkAbgAgAHAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMALgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA4AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADUALAAgADgALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsAHMAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsACAAdQBzAGUAZAAgAGEAcwAgAGYAdQBlAGwAKQAsACAAZQAuAGcALgAgAGwAdQBiAHIAaQBjAGEAbgB0AHMAXAAiACwAIAAzADgALgA4ACwAIABcACIAawBsAFwAIgAsACAAMQAzAC4AOQAsACAAMAAuADAALAAgADAALgAwACwAIAAxADMALgA5ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABnAHIAZQBhAHMAZQBzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADMALgA1ACwAIAAwAC4AMAAsACAAMAAuADAALAAgADMALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAHUAZABlACAAbwBpAGwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAcgB1AGQAZQAgAG8AaQBsACAAYwBvAG4AZABlAG4AcwBhAHQAZQBzAFwAIgAsACAANAA1AC4AMwAsACAAXAAiAHQAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgA5AC4AOAA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADYALgA1ACwAIABcACIAdABcACIALAAgADYAMQAuADAALAAgADAALgAwADgALAAgADAALgAyACwAIAA2ADEALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB1AHQAbwBtAG8AdABpAHYAZQAgAGcAYQBzAG8AbABpAG4AZQAgAC8AIABwAGUAdAByAG8AbAAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA4ADAALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIABnAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADMALgAxACwAIABcACIAawBMAFwAIgAsACAANgA3ACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYANwAuADQAMAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADcALgA1ACwAIABcACIAawBMAFwAIgAsACAANgA4AC4AOQAsACAAMAAuADAAMQAsACAAMAAuADIALAAgADYAOQAuADEAMQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgAgAHQAdQByAGIAaQBuAGUAIABmAHUAZQBsACAALwAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdABpAG4AZwAgAG8AaQBsAFwAIgAsACAAMwA3AC4AMwAsACAAXAAiAGsATABcACIALAAgADYAOQAuADUALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA3ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAxACwAIAAwAC4AMgAsACAANwAwAC4AMgAwACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAwADQALAAgADAALgAyACwAIAA3ADMALgA4ADQALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAGEAcgBvAG0AYQB0AGkAYwAgAGgAeQBkAHIAbwBjAGEAcgBiAG8AbgBzAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADcALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA5ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbAB2AGUAbgB0AHMAOgAgAG0AaQBuAGUAcgBhAGwAIAB0AHUAcgBwAGUAbgB0AGkAbgBlACAAbwByACAAdwBoAGkAdABlACAAcwBwAGkAcgBpAHQAcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABwAGUAdAByAG8AbABlAHUAbQAgAGcAYQBzACAAKABMAFAARwApAFwAIgAsACAAMgA1AC4ANwAsACAAXAAiAGsATABcACIALAAgADYAMAAuADIALAAgADAALgAyACwAIAAwAC4AMgAsACAANgAwAC4ANgAwACwAIAAyADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHAAaAB0AGgAYQBcACIALAAgADMAMQAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAA2ADkALgA4ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAZgBpAG4AZQByAHkAIABnAGEAcwAgAGEAbgBkACAAbABpAHEAdQBpAGQAcwBcACIALAAgADQAMgAuADkALAAgAFwAIgB0AFwAIgAsACAANQA0AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAANQA0AC4ANwA2ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAYwBvAGsAZQBcACIALAAgADMANAAuADIALAAgAFwAIgB0AFwAIgAsACAAOQAyAC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADkAMgAuADgAOAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMgAsACAAMAAuADEALAAgADYAOQAuADkAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA0AC4ANgAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAHQAaABhAG4AbwBsACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGEAIABmAHUAZQBsACAAaQBuACAAYQBuACAAaQBuAHQAZQByAG4AYQBsACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGUAbgBnAGkAbgBlAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQAgAGEAbgBkACAAYgBlAGwAbwB3AFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADAALgAyADIALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMwAwACwAIABcACIATgBFAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwAgAGkAbgAgAGQAaQBmAGYAZQByAGUAbgB0ACAAdAByAGEAbgBzAHAAbwByAHQAIABlAHEAdQBpAHAAbQBlAG4AdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIANgAsACAAMQAwACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBwAG8AcgB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQBcACIALAAgADMANAAuADIALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgA0ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA3AC4ANgAyACwAIAAxADcALgAyACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAwADEALAAgADAALgA1ACwAIAA3ADAALgA0ADEALAAgADEANwAuADMALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAcABlAHQAcgBvAGwAZQB1AG0AIABnAGEAcwAgACgATABQAEcAKQBcACIALAAgADIANgAuADIALAAgAFwAIgBrAGwAXAAiACwAIAA2ADAALgAyACwAIAAwAC4ANQAsACAAMAAuADMALAAgADYAMQAuADAAMAAsACAAMgAwAC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsAbABcACIALAAgADcAMwAuADYALAAgADAALgAwADgALAAgADAALgA1ACwAIAA3ADQALgAxADgALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEUAdABoAGEAbgBvAGwAXAAiACwAIAAyADMALgA0ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAyACwAIAAwAC4AMgAsACAAMAAuADQALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgADMANAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA1ACwAIAAwAC4ANQAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATwB0AGgAZQByACAAYgBpAG8AZgB1AGUAbABzAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AOAAsACAAMQAuADcALAAgADIALgA1ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAGcAaAB0ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADIANQAuADMALAAgAFwAIgBrAGwAXAAiACwAIAA1ADEALgA0ACwAIAA3AC4AMwAsACAAMAAuADMALAAgADUAOQAuADAALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAAMgAuADgALAAgADAALgAzACwAIAA1ADQALgA1ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAA3ACwAIAAwAC4ANAAsACAANwAwAC4AMwA3ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMQAsACAAMAAuADQALAAgADcAMAAuADQALAAgADEANwAuADMALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAIAAtACAARQB1AHIAbwAgAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA0ACwAIAA3ADAALgA1ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAANwAsACAAMAAuADQALAAgADAALgA0ADcALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgA0ACwAIAAwAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAIAATICAARQB1AHIAbwAgAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAyACwAIAAwAC4ANAAsACAAMAAuADYALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwAzAC4AMQAsACAAXAAiAGsAbABcACIALAAgADYANwAuADAALAAgADAALgAwADYALAAgADAALgA2ACwAIAA2ADcALgA2ADYALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIASwBlAHIAbwBzAGUAbgBlACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGYAdQBlAGwAIABpAG4AIABhAG4AIABhAGkAcgBjAHIAYQBmAHQAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAMQAsACAAMAAuADYALAAgADcAMAAuADIAMQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMQAsACAAMAAuADYALAAgADAALgA2ADEALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMQAwAC4AMQAsACAAMAAuADMALAAgAFwAIgBcACIALAAgADEANwAuADIALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARgB1AGUAbAAgAE8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAyACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAMQA4AC4AMAAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBmAGYALQByAG8AYQBkACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACAAYQBuAGQAIABmAG8AcgBlAHMAdAByAHkAIABlAHEAdQBpAHAAbQBlAG4AdABcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAzACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAMQA3AC4AMwAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAATwBmAGYALQByAGEAZAAgAGUAcQB1AGkAcABtAGUAbgB0ACAAYQBuAGQAIAB2AGUAcwBzAGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABPAGYAZgAtAHIAbwBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAIABpAG4AIABvAGYAZgAtAHIAbwBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlACAAcQBcACIALAAgAFwAIgBFAEMAVAByAGEAbgBzACwAcQAgACgARwBKAC8AawBMACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEMATwAyACAARQBGAFQAcgBhAG4ALAAxACwAdABxAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABDAEgANAAgAEUARgBUAHIAYQBuACwAMQAsAHQAZwBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAATgAyAE8AIABFAEYAVAByAGEAbgAsADEALAB0AGcAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUARgBUAHIAYQBuAHMALAAzACwAcQAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIAUABlAHQAcgBvAGwAXAAiACwAIAAzADQALgAyACwAIAA2ADcALgA0ACwAIAAxADAALgAxACwAIAAwAC4AMwAsACAAMQA3AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIARgB1AGUAbAAgAE8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAANwAzAC4ANgAsACAAMAAuADIALAAgADAALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBmAGYALQByAG8AYQBkACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACAAYQBuAGQAIABmAG8AcgBlAHMAdAByAHkAIABlAHEAdQBpAHAAbQBlAG4AdABcACIALAAgAFwAIgBEAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgADYAOQAuADkALAAgADAALgAzACwAIAAwAC4ANQAsACAAMQA3AC4AMwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBGAHUAZQBsAF8ARwBlAHQAVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABTAHQAcgBpAG4AZwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALABcAG4AIAAgACAAIABMAEUARgBUACgAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsACAAXAAiACwAQwBlAGwAbAApACAALQAxACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAXABuACAAIAAgACAAUgBJAEcASABUACgAQwBlAGwAbAAsAEwARQBOACgAQwBlAGwAbAApAC0ARgBJAE4ARAAoAFwAIgAsACAAXAAiACwAQwBlAGwAbAApACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAFwAbgA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALAAgAEYAdQBlAGwAVQBzAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlACwAIABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFQAeQBwAGUALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAUwBVAE0AKABcAG4AIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAEYAdQBlAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACAAPQAgAEYAdQBlAGwAVAB5AHAAZQApACAAKgAgAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFUAcwBlACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgADAAXABuACAAIAApAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AOAA6ACAARgB1AGUAbAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgALgAxACAARgB1AGUAbAAgAFUAcwBlACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAAZgB1AGUAbABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRACwAIABFAEMALAAgAEUARgAsAFwAbgAgACAAIAAgACgAUQAgACoAIABFAEMAIAAqACAARQBGACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAbgBRACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAARwBKAC8AawBMAFwAbgBFAEYAIAA6ACAAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFQAcgBhAG4AcwB0AHEALAAgAEUAQwBfAFQAcgBhAG4AcwBxACwAIABFAEYAXwBUAHIAYQBuAHMAMQB0AHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAyAC4AMwAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB0ACAAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBxAFwAXABsAGUAZgB0ACgAUQBfAHsAVAByAGEAbgBzACwAdABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAVAByAGEAbgBzACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFQAcgBhAG4AcwAsADEALAB0AHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFQAcgBhAG4AcwB0AHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIABjAG8AbQBiAHUAcwB0AGUAZAAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIALAAgAFwAIgBWAGEAcgBpAGUAcwAgAGIAYQBzAGUAZAAgAG8AbgAgAGYAdQBlAGwAIAB0AHkAcABlADoAIABrAEwALAAgAG0AMwAsACAARwBKAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AVAByAGEAbgBzAHEAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AVAByAGEAbgBzADEAdABxAGcAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBcACIALAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAHUAcwBlAGQAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABrAEwAXABuAEUAQwAgADoAIABFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAIAA6ACAAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AUwBDAHEALAAgAEUAQwBfAFMAQwBxACwAIABFAEYAXwBTAEMAMQBxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA4AC4AMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADIAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcwBvAHUAcgBjAGUAcwAgAC0AIABDAGEAbABjAHUAbABhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFMAQwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUwBDACwAMQAsAHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AUwBDAHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFMAQwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AUwBDADEAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBxAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBDAFwAIgAsACAAXAAiAFMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADkAOgAgAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADkALgAxACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXABuAFQAaABlACAAdABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGkAbgBnACAAZAB1AHIAaQBuAGcAIABvAHAAZQByAGEAdABpAG8AbgAgACgAbgBvAHQAIABkAHUAcgBpAG4AZwAgAGkAbgBzAHQAYQBsAGwAYQB0AGkAbwBuACAAbwByACAAZABpAHMAcABvAHMAYQBsACkAXABuAEcAVwBQAFIAIAA6ACAARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSACAAOgAgAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAGMAaABhAHIAZwBlAF8AUgBhACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAGMAbwBuAHQAYQBpAG4AZQBkACAAaQBuACAAYQBwAHAAbABpAGEAbgBjAGUAIABhACAAOgAgAGsAZwBcAG4AbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAgADoAIABQAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAHQAbwB0AGEAbAAgAGMAaABhAHIAZwBlACAAbABlAGEAawBlAGQAIABmAHIAbwBtACAAYQBwAHAAbABpAGEAbgBjAGUAIABhACAAZQBhAGMAaAAgAHkAZQBhAHIAIAA6ACAAUABlAHIAYwBlAG4AdABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYwBoAGEAcgBnAGUAXwBSAGEALAAgAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALABcAG4AIAAgACAAIAAoAGMAaABhAHIAZwBlAF8AUgBhACAAKgAgACgAbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAvADEAMAAwACkAKQAgACoAIAAxADAAIABeACAALQAgADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AUgAsACAARwBXAFAAXwBSACwAXABuACAAIAAgACAAKAAoAEUAXwBSACAAKgAgADEAMABeADMAKQAgACoAIABHAFcAUABfAFIAKQAgACoAIAAxADAAXgAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABoAGUAIAB0AG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGwAZQBhAGsAaQBuAGcAIABkAHUAcgBpAG4AZwAgAG8AcABlAHIAYQB0AGkAbwBuACAAKABuAG8AdAAgAGQAdQByAGkAbgBnACAAaQBuAHMAdABhAGwAbABhAHQAaQBvAG4AIABvAHIAIABkAGkAcwBwAG8AcwBhAGwAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGwAZQBhAGsAYQBnAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAFIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAZwBhAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAzAC4AMQAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABpAG4AZAB1AHMAdAByAGkAYQBsACAAcAByAG8AYwBlAHMAcwBlAHMAIABlAG0AaQBzAHMAaQBvAG4AcwAgAC0AIABSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGEAZwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGMAaABhAHIAZwBlAF8AUgBhACAAKgAgACgAbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAvADEAMAAwACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBSACAAPQAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AYQAgAFwAXABsAGUAZgB0ACgAIABjAGgAYQByAGcAZQBfAHsAUgBhAH0AIABcAFwAdABpAG0AZQBzACAAXABcAGYAcgBhAGMAewBsAGUAYQBrAGEAZwBlAFwAXAAsAHIAYQB0AGUAXwBhAH0AewAxADAAMAB9ACAAXABcAHIAaQBnAGgAdAApACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMATwAyAGUAIAA9ACAAXABcAGwAZQBmAHQAKABFAF8AUgAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7ADMAfQAgAFwAXAByAGkAZwBoAHQAKQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAFIAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAaABhAHIAZwBlAF8AUgBhAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAGMAbwBuAHQAYQBpAG4AZQBkACAAaQBuACAAYQBwAHAAbABpAGEAbgBjAGUAIABhAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEAXAAiACwAIABcACIAUAByAGMAZQBuAHQAYQBnAGUAIABvAGYAIAB0AG8AdABhAGwAIABjAGgAYQByAGcAZQAgAGwAZQBhAGsAZQBkACAAZgByAG8AbQAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgAGUAYQBjAGgAIAB5AGUAYQByAFwAIgAsACAAXAAiAFAAZQByAGMAZQBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBhAFwAIgAsACAAXAAiAEEAcABwAGwAaQBhAG4AYwBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXAAiACwAIABcACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAF8AUgBcACIALAAgAFwAIgBUAG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAXAAiACwAIABcACIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGcAYQBzAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAOQAuADEALgAxACAAKAAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAF8AUgBcACIALAAgAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAXAAiACwAIABcACIARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABlAHEAdQBhAHQAaQBvAG4AIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAHQAbwAgAEMATwAyAC0AZQAgAHUAcwBpAG4AZwAgAHQAaABlACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0AFwAdQAwADAAMgA3AHMAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgACgARwBXAFAAKQAuAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEEAcABwAGUAbgBkAGkAeAAgADIAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzADoAIABUAGEAYgBsAGUAIAAyADMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsAHMAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABBAHAAcABlAG4AZABpAHgAIAAyACAALQAgAFQAYQBiAGwAZQAgADIAMwBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwA5ACwAIAA1ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAaABlAG0AaQBjAGEAbAAgAGYAbwByAG0AdQBsAGEAXAAiACwAIABcACIARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIAAoAEEAUgA1ACkAXAAiACwAIABcACIARwBhAHMAIAAtACAARgBDACAAbgBhAG0AZQBcACIALAAgAFwAIgBBAGQAaQB0AGkAbwBuAGEAbAAgAGQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAXAAiACwAIABcACIAQwBPADIAXAAiACwAIAAxACwAIABcACIAQwBPADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBDAEgANABcACIALAAgADIAOAAsACAAXAAiAEMASAA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAXAAiACwAIABcACIATgAyAE8AXAAiACwAIAAyADYANQAsACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBsAHAAaAB1AHIAIABoAGUAeABhAGYAbAB1AG8AcgBpAGQAZQBcACIALAAgAFwAIgBTAEYANgBcACIALAAgADIAMwA1ADAAMAAsACAAXAAiAFMARgA2AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgAzACAAKABSAC0AMgAzACkAXAAiACwAIABcACIAQwBIAEYAMwBcACIALAAgACAAMQAyADQAMAAwACwAIABcACIASABGAEMALQAyADMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAzADIAIAAoAFIALQAzADIAKQBcACIALAAgAFwAIgBDAEgAMgBGADIAXAAiACwAIAA2ADcANwAsACAAXAAiAEgARgBDAC0AMwAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0ANAAxACAAKABSAC0ANAAxACkAXAAiACwAIABcACIAQwBIADMARgBcACIALAAgACAAMQAxADYALAAgAFwAIgBIAEYAQwAtADQAMQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADQAMwAtADEAMABtAGUAZQAgACgAUgAtADQAMwAxADAAbQBlAGUAKQBcACIALAAgAFwAIgBDADUASAAyAEYAMQAwAFwAIgAsACAAMQA2ADUAMAAsACAAXAAiAEgARgBDAC0ANAAzAC0AMQAwAG0AZQBlAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQAyADUAIAAoAFIALQAxADIANQApAFwAIgAsACAAXAAiAEMAMgBIAEYANQBcACIALAAgACAAMwAxADcAMAAsACAAXAAiAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADMANAAgACgAUgAtADEAMwA0ACkAXAAiACwAIABcACIAQwAyAEgAMgBGADQAIAAoAEMASABGADIAQwBIAEYAMgApAFwAIgAsACAAIAAxADEAMgAwACwAIABcACIASABGAEMALQAxADMANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEAMwA0AGEAIAAoAFIALQAxADMANABhACkAXAAiACwAIABcACIAQwAyAEgAMgBGADQAIAAoAEMASAAyAEYAQwBGADMAKQBcACIALAAgADEAMwAwADAALAAgAFwAIgBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADQAMwAgACgAUgAtADEANAAzACkAXAAiACwAIABcACIAQwAyAEgAMwBGADMAIAAoAEMASABGADIAQwBIADIARgApAFwAIgAsACAAMwAyADgALAAgAFwAIgBIAEYAQwAtADEANAAzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA0ADMAYQAgACgAUgAtADEANAAzAGEAKQBcACIALAAgAFwAIgBDADIASAAzAEYAMwAgACgAQwBGADMAQwBIADMAKQBcACIALAAgADQAOAAwADAALAAgAFwAIgBIAEYAQwAtADEANAAzAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADUAMgBhACAAKABSAC0AMQA1ADIAYQApAFwAIgAsACAAXAAiAEMAMgBIADQARgAyACAAKABDAEgAMwBDAEgARgAyACkAXAAiACwAIAAxADMAOAAsACAAXAAiAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMgA3AGUAYQAgACgAUgAtADIAMgA3AGUAYQApAFwAIgAsACAAXAAiAEMAMwBIAEYANwBcACIALAAgADMAMwA1ADAALAAgAFwAIgBIAEYAQwAtADIAMgA3AGUAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMwA2AGYAYQAgACgAUgAtADIAMwA2AGYAYQApAFwAIgAsACAAXAAiAEMAMwBIADIARgA2AFwAIgAsACAAOAAwADYAMAAsACAAXAAiAEgARgBDAC0AMgAzADYAZgBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgA0ADUAYwBhACAAKABSAC0AMgA0ADUAYwBhACkAXAAiACwAIABcACIAQwAzAEgAMwBGADUAXAAiACwAIAA3ADEANgAsACAAXAAiAEgARgBDAC0AMgA0ADUAYwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgA0ADUAZgBhACAAKABSAC0AMgA0ADUAZgBhACkAXAAiACwAIABcACIAQwBIAEYAMgBDAEgAMgBDAEYAMwBcACIALAAgADgANQA4ACwAIABcACIASABGAEMALQAyADQANQBmAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAzADYANQBtAGYAYwAgACgAUgAtADMANgA1AG0AZgBjACkAXAAiACwAIABcACIAQwBIADMAQwBGADIAQwBIADIAQwBGADMAXAAiACwAIAA4ADAANAAsACAAXAAiAEgARgBDAC0AMwA2ADUAbQBmAGMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADIAMgAgACgAUgAtADIAMgApAFwAIgAsACAAXAAiAEMASABDAGwARgAyAFwAIgAsACAAMQA3ADYAMAAsACAAXAAiAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEAMgAzACAAKABSAC0AMQAyADMAKQBcACIALAAgAFwAIgBDAEgAQwBsADIAMgBDAEYAMwBcACIALAAgADcAOQAsACAAXAAiAEgAQwBGAEMALQAxADIAMwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQAyADQAIAAoAFIALQAxADIANAApAFwAIgAsACAAXAAiAEMASABDAGwARgBDAEYAMwBcACIALAAgADUAMgA3ACwAIABcACIASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADQAMQBiACAAKABSAC0AMQA0ADEAYgApAFwAIgAsACAAXAAiAEMASAAzAEMAQwBsADIARgBcACIALAAgADcAOAAyACwAIABcACIASABDAEYAQwAtADEANAAxAGIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEANAAyAGIAIAAoAFIALQAxADQAMgBiACkAXAAiACwAIABcACIAQwBIADIAQwBDAGwARgAyAFwAIgAsACAAMQA5ADgAMAAsACAAXAAiAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGEAIAAoAFIALQAyADIANQBjAGEAKQBcACIALAAgAFwAIgBDAEgAQwBsADIAQwBGADIAQwBGADMAXAAiACwAIAAxADIANwAsACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADIAMgA1AGMAYgAgACgAUgAtADIAMgA1AGMAYgApAFwAIgAsACAAXAAiAEMASABDAGwARgBDAEYAMgBDAEMASQBGADIAXAAiACwAIAA1ADIANQAsACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAxADQAIABQAGUAcgBmAGwAdQBvAHIAbwBtAGUAdABoAGEAbgBlACAAKAB0AGUAdAByAGEAZgBsAHUAbwByAG8AbQBlAHQAaABhAG4AZQApAFwAIgAsACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAAsACAAXAAiAFAARgBDAC0AMQA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMQAxADYAIABQAGUAcgBmAGwAdQBvAHIAbwBlAHQAaABhAG4AZQAgACgAaABlAHgAYQBmAGwAdQBvAHIAbwBlAHQAaABhAG4AZQApAFwAIgAsACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADEAMQAwADAALAAgAFwAIgBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMgAxADgAIABQAGUAcgBmAGwAdQBvAHIAbwBwAHIAbwBwAGEAbgBlAFwAIgAsACAAXAAiAEMAMwBGADgAXAAiACwAIAA4ADkAMAAwACwAIABcACIAUABGAEMALQAyADEAOABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADMAMQAtADEAMAAgAFAAZQByAGYAbAB1AG8AcgBvAGIAdQB0AGEAbgBlAFwAIgAsACAAXAAiAEMANABGADEAMABcACIALAAgADkAMgAwADAALAAgAFwAIgBQAEYAQwAtADMAMQAtADEAMABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADMAMQA4ACAAUABlAHIAZgBsAHUAbwByAG8AYwB5AGMAbABvAGIAdQB0AGEAbgBlAFwAIgAsACAAXAAiAGMALQBDADQARgA4AFwAIgAsACAAOQA1ADQAMAAsACAAXAAiAFAARgBDAC0AMwAxADgAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA0ADEALQAxADIAIABQAGUAcgBmAGwAdQBvAHIAbwBwAGUAbgB0AGEAbgBlAFwAIgAsACAAXAAiAEMANQBGADEAMgBcACIALAAgADgANQA1ADAALAAgAFwAIgBQAEYAQwAtADQAMQAtADEAMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADUAMQAtADEANAAgAFAAZQByAGYAbAB1AG8AcgBvAGgAZQB4AGEAbgBlAFwAIgAsACAAXAAiAEMANgBGADEANABcACIALAAgADcAOQAxADAALAAgAFwAIgBQAEYAQwAtADUAMQAtADEANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADkAMQAtADEAOAAgAFAAZQByAGYAbAB1AG4AYQBmAGUAbgBlAFwAIgAsACAAXAAiAEMAMQAwAEYAMQA4AFwAIgAsACAANwAxADkAMAAsACAAXAAiAFAARgBDAC0AOQAxAC0AMQA4AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAyAFwAIgAsACAAXAAiAEMAQwBsADIARgAyAFwAIgAsACAAMQAwADIAMAAwACwAIABcACIAQwBGAEMALQAxADIAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMwBcACIALAAgAFwAIgBDAEMAbABGADMAXAAiACwAIAAxADMAOQAwADAALAAgAFwAIgBDAEYAQwAtADEAMwBcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAQwBDAGwARgAyAEMAQwBsAEYAMgBcACIALAAgADgANQA5ADAALAAgAFwAIgBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADEANQBcACIALAAgAFwAIgBDAEMAbABGADIAQwBGADMAXAAiACwAIAA3ADYANwAwACwAIABcACIAQwBGAEMALQAxADEANQBcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBHAEEAUwAgAC0AIABGAEMAIABuAGEAbQBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAdAByAHUAbgBjAGEAdABlAGQAIABnAGEAcwAgAG4AYQBtAGUAIAB0AG8AIABhAGwAbABvAHcAIABtAGEAdABjAGgAaQBuAGcAIAB3AGkAdABoACAAbwB0AGgAZQByACAAdABhAGIAbABlAHMALgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAGcAYQBzAGUAcwAgAGYAcgBvAG0AIABJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBBAGQAZABpAHQAaQBvAG4AYQBsACAAZABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4ALgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEEAcABwAGUAbgBkAGkAeAAgADIAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzADoAIABCAGwAZQBuAGQAZQBkACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQgBsAGUAbgBkAGUAZAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABzACAAKABtAGEAbgB5ACAAYwBvAG4AdABhAGkAbgBpAG4AZwAgAEgARgBDAFMAIABhAG4AZAAvAG8AcgAgAFAARgBDAFMAKQBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAEEAcABwAGUAbgBkAGkAeAAgADIAIAAtACAAVABhAGIAbABlACAAMgA0AFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ADEALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBsAGUAbgBkAFwAIgAsACAAXAAiAEMAbwBuAHMAdABpAHQAdQBlAG4AdABzAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAGkAdABpAG8AbgAgACgAJQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMABcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAUgAtADQAMAAwACAAYwBhAG4AIABoAGEAdgBlACAAdgBhAHIAaQBvAHUAcwAgAHAAcgBvAHAAbwByAHQAaQBvAG4AcwAgAG8AZgAgAEMARgBDAC0AMQAyACAAYQBuAGQAIABDAEYAQwAtADEAMQA0AC4AIABUAGgAZQAgAGUAeABhAGMAdAAgAGMAbwBtAHAAbwBzAGkAdABpAG8AbgAgAG4AZQBlAGQAcwAgAHQAbwAgAGIAZQAgAHMAcABlAGMAaQBmAGkAZQBkACwAIABlAC4AZwAuACwAIABSAC0ANAAwADAAIAAoADYAMAAvADQAMAApAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAxAEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgAoADUAMwAuADAALwAxADMALgAwAC8AMwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMQBCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAKAA2ADEALgAwAC8AMQAxAC4AMAAvADIAOAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADEAQwBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiACgAMwAzAC4AMAAvADEANQAuADAALwA1ADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAyAEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADYAMAAuADAALwAyAC4AMAAvADMAOAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADIAQgBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABDAC0AMgA5ADAALwBIAEMARgBDAC0AMgAyAFwAIgAsACAAXAAiACgAMwA4AC4AMAAvADIALgAwAC8ANgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMwBBAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAKAA1AC4AMAAvADcANQAuADAALwAyADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAzAEIAXAAiACwAIABcACIASABDAC0AMgA5ADAALwBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOABcACIALAAgAFwAIgAoADUALgAwAC8ANQA2AC4AMAAvADMAOQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADQAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADQAMwBhAC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgANAA0AC4AMAAvADUAMgAuADAALwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwAgAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADQAMgBiAC8AUABGAEMALQAzADEAOABcACIALAAgAFwAIgAoADQANQAuADAALwA3AC4AMAAvADUALgA1AC8ANAAyAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANgBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEMALQA2ADAAMABhAC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA1ADUALgAwAC8AMQA0AC4AMAAvADQAMQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcAQQBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAyADAALgAwAC8ANAAwAC4AMAAvADQAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcAQgBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAxADAALgAwAC8ANwAwAC4AMAAvADIAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcAQwBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAyADMALgAwAC8AMgA1AC4AMAAvADUAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcARABcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAxADUALgAwAC8AMQA1AC4AMAAvADcAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcARQBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAyADUALgAwAC8AMQA1AC4AMAAvADYAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADgAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADQAMwBhAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADcALgAwAC8ANAA2AC4AMAAvADQANwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADkAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA2ADAALgAwAC8AMgA1AC4AMAAvADEANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADkAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA2ADUALgAwAC8AMgA1AC4AMAAvADEAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADAAQQBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAKAA1ADAALgAwAC8ANQAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMABCAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQBcACIALAAgAFwAIgAoADQANQAuADAALwA1ADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAxAEEAXAAiACwAIABcACIASABDAC0AMQAyADcAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAxAC4ANQAvADgANwAuADUALwAxADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAxAEIAXAAiACwAIABcACIASABDAC0AMQAyADcAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAzAC4AMAAvADkANAAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBDAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMwAuADAALwA5ADUALgA1AC8AMQAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADIAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANwAwAC4AMAAvADUALgAwAC8AMgA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMwBBAFwAIgAsACAAXAAiAFAARgBDAC0AMgAxADgALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgAOQAuADAALwA4ADgALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADQAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQAxAC4AMAAvADIAOAAuADUALwA0AC4AMAAvADEANgAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADQAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQAwAC4AMAAvADMAOQAuADAALwAxAC4ANQAvADkALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA1AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADgAMgAuADAALwAxADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA1AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADIANQAuADAALwA3ADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA2AEEAXAAiACwAIABcACIASABGAEMALQAxADMANABhAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAC0ANgAwADAAXAAiACwAIABcACIAKAA1ADkALgAwAC8AMwA5AC4ANQAvADEALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA3AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQAvAEgAQwAtADYAMAAwAFwAIgAsACAAXAAiACgANAA2AC4ANgAvADUAMAAuADAALwAzAC4ANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAOABBAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADEALgA1AC8AOQA2AC4AMAAvADIALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA5AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQAvAEgARQAtAEUAMQA3ADAAXAAiACwAIABcACIAKAA3ADcALgAwAC8AMQA5AC4AMAAvADQALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMgAwAEEAXAAiACwAIABcACIASABGAEMALQAxADMANABhAC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA4ADgALgAwAC8AMQAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMQBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAA1ADgALgAwAC8ANAAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgAOAA1AC4AMQAvADEAMQAuADUALwAzAC4ANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMgBCAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgANQA1AC4AMAAvADQAMgAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMgBDAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgAOAAyAC4AMAAvADEANQAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMABcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADcAMwAuADgALwAyADYALgAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAxAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBDAEYAQwAtADEAMgBcACIALAAgAFwAIgAoADcANQAuADAALwAyADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAyAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBDAEYAQwAtADEAMQA1AFwAIgAsACAAXAAiACgANAA4AC4AOAAvADUAMQAuADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADMAXAAiACwAIABcACIASABGAEMALQAyADMALwBDAEYAQwAtADEAMwBcACIALAAgAFwAIgAoADQAMAAuADEALwA1ADkALgA5ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA0AFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8AQwBGAEMALQAxADEANQBcACIALAAgAFwAIgAoADQAOAAuADIALwA1ADEALgA4ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA1AFwAIgAsACAAXAAiAEMARgBDAC0AMQAyAC8ASABDAEYAQwAtADMAMQBcACIALAAgAFwAIgAoADcAOAAuADAALwAyADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA2AFwAIgAsACAAXAAiAEMARgBDAC0AMwAxAC8AQwBGAEMALQAxADEANABcACIALAAgAFwAIgAoADUANQAuADEALwA0ADQALgA5ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA3AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQBcACIALAAgAFwAIgAoADUAMAAuADAALwA1ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA4AEEAXAAiACwAIABcACIASABGAEMALQAyADMALwBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiACgAMwA5AC4AMAAvADYAMQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADgAQgBcACIALAAgAFwAIgBIAEYAQwAtADIAMwAvAFAARgBDAC0AMQAxADYAXAAiACwAIABcACIAKAA0ADYALgAwAC8ANQA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAOQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiACgANAA0AC4AMAAvADUANgAuADAAKQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABjAGgAYQBuAGcAZQBkACAASABDADYAMAAwAGEAIAB0AG8AIABIAEMALQA2ADAAMABhACAAZgBvAHIAIABiAGwAZQBuAGQAIABSAC0ANAAxADQAQgAuACAARgBpAHgAZQBkACAAdAB5AHAAbwAgAGYAbwByACAAYgBsAGUAbgBkACAAUgAtADQAMAA1AEEAIAAtACAAQwBoAGEAbgBnAGUAZAAgAEgAQwBGAEMAMQA0ADIAYgAgAHQAbwAgAEgAQwBGAEMALQAxADQAMgBiAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ATABlAGEAawBhAGcAZQAgAHIAYQB0AGUAcwAgAGYAbwByACAAYwBvAG0AbQBvAG4AIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuACAAYQBuAGQAIABhAGkAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEkAbgBkAGkAYwBhAHQAaQB2AGUAIABsAGUAYQBrAGEAZwBlACAAcgBhAHQAZQBzACAAZgBvAHIAIABjAG8AbQBtAG8AbgAgAHIAZQBmAHIAaQBnAGUAcgBhAHQAaQBvAG4AIABhAG4AZAAgAGEAaQByACAALQAgAGMAbwBuAGQAaQB0AGkAbwBuAGkAbgBnACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAMQAwAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAGwAZQBhAGsAYQBnAGUAIAByAGEAdABlACAAKAAlACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAcgBlAGYAcgBpAGcAZQByAGEAdABvAHIAcwBcACIALAAgADEALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuAFwAIgAsACAAMQA1AC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAEEALwBDACAAcABvAHIAdABhAGIAbABlAFwAIgAsACAAMgAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIABBAC8AQwAgAHMAcABsAGkAdABcACIALAAgADMALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAQQAvAEMAIABwAGEAYwBrAGEAZwBlAGQAXAAiACwAIAAyAC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAHYAZQBoAGkAYwBsAGUAIABBAC8AQwBcACIALAAgADYALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAdgBlAGgAaQBjAGwAZQAgAEEALwBDAFwAIgAsACAAMQAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBhAGwAYwB1AGwAYQB0AGUAQgBsAGUAbgBkAEcAVwBQAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMQAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMgAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMwAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAANAAsAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAxACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAyACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAzACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAA0ACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVQBuAGkAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVABpAHQAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFUAbgBpAHQAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVABpAHQAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGEAdABhACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAYQBsAGMAdQBsAGEAdABlAEIAbABlAG4AZABHAFcAUAAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -19998,31 +20000,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADQALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAxACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzACAAaQBuAGMAbAB1AGQAaQBuAGcAIABsAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgACAAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA1AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAIAAoAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwAKQBcACIALAAgAFwAIgBGAHUAZQBsACAAdQBuAGkAdABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAE8AMgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAEgANABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABOADIATwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAG8AbQBiAGkAbgBlAGQAIABnAGEAcwBlAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAyACwAIAAwAC4AMAAzACwAIAA1ADEALgA2ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAbQBpAG4AZQAgAHcAYQBzAHQAZQAgAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4AOQAsACAANAAuADYALAAgADAALgAzACwAIAA1ADYALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAoAHIAZQB2AGUAcgB0AGkAbgBnACAAdABvACAAcwB0AGEAbgBkAGEAcgBkACAAYwBvAG4AZABpAHQAaQBvAG4AcwApAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVQBuAHAAcgBvAGMAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAA2ADIAOQAsACAAXAAiAG0AMwBcACIALAAgADUANgAuADUALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANgAuADUANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBrAGUAIABvAHYAZQBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAxADgAMQAsACAAXAAiAG0AMwBcACIALAAgADMANwAuADAALAAgADAALgAwADMALAAgADAALgAwADUALAAgADMANwAuADAAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABhAHMAdAAgAGYAdQByAG4AYQBjAGUAIABnAGEAcwBcACIALAAgADAALgAwADAANAAwACwAIABcACIAbQAzAFwAIgAsACAAMgAzADQALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAAyACwAIAAyADMANAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADAANAAsACAAMAAuADAAMwAsACAANgAwAC4AMgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBMAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAGUAbwB1AHMAIABmAG8AcwBzAGkAbAAgAGYAdQBlAGwAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA5ADAALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABhAG4AZABmAGkAbABsACAAYgBpAG8AZwBhAHMAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtAGUAdABoAGEAbgBlACAAbwBuAGwAeQApAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAsACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAwAC4AMAAzADcAMAAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAG0AZQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAAMAAuADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAeQBkAHIAbwBnAGUAbgBcACIALAAgADAALgAwADEAMgAyACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADAALgAwACwAIAAwAC4ANQAsACAAMAAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIAAxACwAIABcACIARwBKAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIAB3AGUAcgBlACAAYQBkAGQAZQBkACwAIABlAGEAYwBoACAAdwBpAHQAaAAgAGEAbgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAMQAgAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwALgAgAFQAaABpAHMAIABpAHMAIABmAG8AcgAgAHUAcwBlAHIAcwAgAHcAaABvACAAaABhAHYAZQAgAGYAdQBlAGwAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABkAGEAdABhACAAaQBuACAARwBKACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbQAzAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA2AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAdABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE0AZQB0AHIAbwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAATgBhAHQAdQByAGEAbAAgAEcAYQBzACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgBvAG4AIAAtACAATQBlAHQAcgBvAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgADQALgAwACwAIAA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIAA4AC4AOAAsACAANwAuADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADEAMAAuADcALAAgADEAMAAuADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAA0AC4AMQAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgADQALgAxACwAIAA0AC4AMABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAE4AUwBXACAAYQBuAGQAIABBAEMAVAAgAHMAcABsAGkAdAAgAGkAbgB0AG8AIABzAGUAcABhAHIAYQB0AGUAIAByAG8AdwBzAC4AIABcAHUAMAAwADIANwBDAFwAdQAwADAAMgA3ACAAVgBhAGwAdQBlAHMAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAGEAbgBkACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAdABoAG8AcwBlACAAZgBvAHIAIABWAGkAYwB0AG8AcgBpAGEAIABhAG4AZAAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAHIAZQBzAHAAZQBjAHQAaQB2AGUAbAB5AC4AIAAoAFMAZQBlACAAYQBwAHAAZQBuAGQAaQBjAGUAcwApAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEEAcwAgAFMAYwBvAHAAZQAgADMAIABmAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAYQB0ACAAdABoAGUAIABwAG8AaQBuAHQAIAB3AGgAZQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABpAHMAIABkAGUAbABpAHYAZQByAGUAZAAgAHQAbwAgAGUAbgBkACAAdQBzAGUAcgBzACwAIABpAHQAIABpAHMAIABuAGUAYwBlAHMAcwBhAHIAeQAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAYQB0ACAAZQBhAGMAaAAgAG8AZgAgAHQAaABlACAAbABvAGEAZAAgAGMAZQBuAHQAcgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBHAGEAcwAgAHIAZQBhAGMAaABlAHMAIABlAG4AZAAgAHUAcwBlAHIAcwAgAGUAaQB0AGgAZQByACAAZgByAG8AbQAgAHQAaABlACAAbQBlAHQAcgBvACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABuAGUAdAB3AG8AcgBrAHMAIABvAHIAIABkAGkAcgBlAGMAdAAgAGYAcgBvAG0AIAB0AGgAZQAgAGgAaQBnAGgAIAAtACAAcAByAGUAcwBzAHUAcgBlACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABwAGkAcABlAGwAaQBuAGUAcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAEgAbwB1AHMAZQBoAG8AbABkAHMAIABhAG4AZAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB1AHMAZQByAHMAIAB0AGUAbgBkACAAdABvACAAYgBlACAAcwBlAHIAdgBlAGQAIABiAHkAIAB0AGgAZQAgAGYAbwByAG0AZQByACwAIABhAG4AZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAGcAZQBuAGUAcgBhAHQAbwByAHMAIABhAG4AZAAgAGwAYQByAGcAZQAgAGkAbgBkAHUAcwB0AHIAaQBhAGwAIABwAGwAYQBuAHQAcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGwAYQB0AHQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBNAGUAdAByAG8AIABpAHMAIABkAGUAZgBpAG4AZQBkACAAYQBzACAAbABvAGMAYQB0AGUAZAAgAG8AbgAgAG8AcgAgAGUAYQBzAHQAIABvAGYAIAB0AGgAZQAgAGQAaQB2AGkAZABpAG4AZwAgAHIAYQBuAGcAZQAgAGkAbgAgAE4AUwBXACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAEMAYQBuAGIAZQByAHIAYQAgAGEAbgBkACAAUQB1AGUAYQBuAGIAZQB5AGEAbgAsACAATQBlAGwAYgBvAHUAcgBuAGUALAAgAEIAcgBpAHMAYgBhAG4AZQAsACAAQQBkAGUAbABhAGkAZABlACAAbwByACAAUABlAHIAdABoAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIATwB0AGgAZQByAHcAaQBzAGUALAAgAHQAaABlACAAbgBvAG4AIAAtACAAbQBlAHQAcgBvACAAZgBhAGMAdABvAHIAIABzAGgAbwB1AGwAZAAgAGIAZQAgAHUAcwBlAGQALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEYAYQBjAHQAbwByAHMAIABhAHIAZQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAGEAbABsACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAHcAaABpAGMAaAAgAG0AYQB5ACAAaQBuAGMAbAB1AGQAZQAgAGMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIAVABhAGIAbABlACAANgAgAGkAcwAgAG4AbwB0ACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHQAbwAgAGUAdABoAGEAbgBlAC4AIABTAGUAZQAgAFQAYQBiAGwAZQAgADcAIABJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEMAIAA9ACAAQwBvAG4AZgBpAGQAZQBuAHQAaQBhAGwALgAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAHQAaABlACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIABhAHIAZQAgAG4AbwB0ACAAYQB2AGEAaQBsAGEAYgBsAGUAIABkAHUAZQAgAHQAbwAgAGMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAGkAdAB5ACAAYwBvAG4AcwB0AHIAYQBpAG4AdABzACAAdABoAGEAdAAgAGEAcgBpAHMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAGEAIABsAGkAbQBpAHQAZQBkACAAbgB1AG0AYgBlAHIAIABvAGYAIABOAEcARQBSACAAZABhAHQAYQAgAGkAbgBwAHUAdABzAC4AIABJAHQAIABpAHMAIABzAHUAZwBnAGUAcwB0AGUAZAAgAHQAaABhAHQAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAHQAaABlACAAdQBzAGUAIABvAGYAIAB0AGgAZQAgAFYAaQBjAHQAbwByAGkAYQBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGkAcwAgAGEAcABwAHIAbwBwAHIAaQBhAHQAZQAsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAHcAaABpAGwAZQAgAGYAbwByACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZABvACAAbgBvAHQAIABpAG4AYwBsAHUAZABlACAAZgB1AGcAaQB0AGkAdgBlACAAZQBtAGkAcwBzAGkAbwBuACAAbABlAGEAawBhAGcAZQAgAGYAcgBvAG0AIABsAG8AdwAgAHAAcgBlAHMAcwB1AHIAZQAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlACAAbgBlAHQAdwBvAHIAawBzACAAdwBoAGkAbABlACAAdABoAG8AcwBlACAAZgByAG8AbQAgAGgAaQBnAGgAIABwAHIAZQBzAHMAdQByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZwBhAHMAIABuAGUAdAB3AG8AcgBrAHMAIABhAHIAZQAgAGMAbwBuAHMAaQBkAGUAcgBlAGQAIABuAGUAZwBsAGkAZwBpAGIAbABlAC4AXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMALAAgAGkAbgBjAGwAdQBkAGkAbgBnACAAYwBlAHIAdABhAGkAbgAgAHAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMALgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA4AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADUALAAgADgALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsAHMAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsACAAdQBzAGUAZAAgAGEAcwAgAGYAdQBlAGwAKQAsACAAZQAuAGcALgAgAGwAdQBiAHIAaQBjAGEAbgB0AHMAXAAiACwAIAAzADgALgA4ACwAIABcACIAawBsAFwAIgAsACAAMQAzAC4AOQAsACAAMAAuADAALAAgADAALgAwACwAIAAxADMALgA5ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABnAHIAZQBhAHMAZQBzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADMALgA1ACwAIAAwAC4AMAAsACAAMAAuADAALAAgADMALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAHUAZABlACAAbwBpAGwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAcgB1AGQAZQAgAG8AaQBsACAAYwBvAG4AZABlAG4AcwBhAHQAZQBzAFwAIgAsACAANAA1AC4AMwAsACAAXAAiAHQAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgA5AC4AOAA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADYALgA1ACwAIABcACIAdABcACIALAAgADYAMQAuADAALAAgADAALgAwADgALAAgADAALgAyACwAIAA2ADEALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB1AHQAbwBtAG8AdABpAHYAZQAgAGcAYQBzAG8AbABpAG4AZQAgAC8AIABwAGUAdAByAG8AbAAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA4ADAALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIABnAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADMALgAxACwAIABcACIAawBMAFwAIgAsACAANgA3ACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYANwAuADQAMAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADcALgA1ACwAIABcACIAawBMAFwAIgAsACAANgA4AC4AOQAsACAAMAAuADAAMQAsACAAMAAuADIALAAgADYAOQAuADEAMQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgAgAHQAdQByAGIAaQBuAGUAIABmAHUAZQBsACAALwAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdABpAG4AZwAgAG8AaQBsAFwAIgAsACAAMwA3AC4AMwAsACAAXAAiAGsATABcACIALAAgADYAOQAuADUALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA3ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAxACwAIAAwAC4AMgAsACAANwAwAC4AMgAwACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAwADQALAAgADAALgAyACwAIAA3ADMALgA4ADQALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAGEAcgBvAG0AYQB0AGkAYwAgAGgAeQBkAHIAbwBjAGEAcgBiAG8AbgBzAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADcALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA5ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbAB2AGUAbgB0AHMAOgAgAG0AaQBuAGUAcgBhAGwAIAB0AHUAcgBwAGUAbgB0AGkAbgBlACAAbwByACAAdwBoAGkAdABlACAAcwBwAGkAcgBpAHQAcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABwAGUAdAByAG8AbABlAHUAbQAgAGcAYQBzACAAKABMAFAARwApAFwAIgAsACAAMgA1AC4ANwAsACAAXAAiAGsATABcACIALAAgADYAMAAuADIALAAgADAALgAyACwAIAAwAC4AMgAsACAANgAwAC4ANgAwACwAIAAyADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHAAaAB0AGgAYQBcACIALAAgADMAMQAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAA2ADkALgA4ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAZgBpAG4AZQByAHkAIABnAGEAcwAgAGEAbgBkACAAbABpAHEAdQBpAGQAcwBcACIALAAgADQAMgAuADkALAAgAFwAIgB0AFwAIgAsACAANQA0AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAANQA0AC4ANwA2ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAYwBvAGsAZQBcACIALAAgADMANAAuADIALAAgAFwAIgB0AFwAIgAsACAAOQAyAC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADkAMgAuADgAOAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMgAsACAAMAAuADEALAAgADYAOQAuADkAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA0AC4ANgAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAHQAaABhAG4AbwBsACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGEAIABmAHUAZQBsACAAaQBuACAAYQBuACAAaQBuAHQAZQByAG4AYQBsACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGUAbgBnAGkAbgBlAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQAgAGEAbgBkACAAYgBlAGwAbwB3AFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADAALgAyADIALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMwAwACwAIABcACIATgBFAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwAgAGkAbgAgAGQAaQBmAGYAZQByAGUAbgB0ACAAdAByAGEAbgBzAHAAbwByAHQAIABlAHEAdQBpAHAAbQBlAG4AdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIANgAsACAAMQAwACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBwAG8AcgB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQBcACIALAAgADMANAAuADIALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgA0ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA3AC4ANgAyACwAIAAxADcALgAyACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAwADEALAAgADAALgA1ACwAIAA3ADAALgA0ADEALAAgADEANwAuADMALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAcABlAHQAcgBvAGwAZQB1AG0AIABnAGEAcwAgACgATABQAEcAKQBcACIALAAgADIANgAuADIALAAgAFwAIgBrAGwAXAAiACwAIAA2ADAALgAyACwAIAAwAC4ANQAsACAAMAAuADMALAAgADYAMQAuADAAMAAsACAAMgAwAC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsAbABcACIALAAgADcAMwAuADYALAAgADAALgAwADgALAAgADAALgA1ACwAIAA3ADQALgAxADgALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEUAdABoAGEAbgBvAGwAXAAiACwAIAAyADMALgA0ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAyACwAIAAwAC4AMgAsACAAMAAuADQALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgADMANAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA1ACwAIAAwAC4ANQAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATwB0AGgAZQByACAAYgBpAG8AZgB1AGUAbABzAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AOAAsACAAMQAuADcALAAgADIALgA1ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAGcAaAB0ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADIANQAuADMALAAgAFwAIgBrAGwAXAAiACwAIAA1ADEALgA0ACwAIAA3AC4AMwAsACAAMAAuADMALAAgADUAOQAuADAALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAAMgAuADgALAAgADAALgAzACwAIAA1ADQALgA1ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAA3ACwAIAAwAC4ANAAsACAANwAwAC4AMwA3ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMQAsACAAMAAuADQALAAgADcAMAAuADQALAAgADEANwAuADMALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAIAAtACAARQB1AHIAbwAgAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA0ACwAIAA3ADAALgA1ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAANwAsACAAMAAuADQALAAgADAALgA0ADcALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgA0ACwAIAAwAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAIAATICAARQB1AHIAbwAgAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAyACwAIAAwAC4ANAAsACAAMAAuADYALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwAzAC4AMQAsACAAXAAiAGsAbABcACIALAAgADYANwAuADAALAAgADAALgAwADYALAAgADAALgA2ACwAIAA2ADcALgA2ADYALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIASwBlAHIAbwBzAGUAbgBlACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGYAdQBlAGwAIABpAG4AIABhAG4AIABhAGkAcgBjAHIAYQBmAHQAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAMQAsACAAMAAuADYALAAgADcAMAAuADIAMQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMQAsACAAMAAuADYALAAgADAALgA2ADEALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMQAwAC4AMQAsACAAMAAuADMALAAgAFwAIgBcACIALAAgADEANwAuADIALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARgB1AGUAbAAgAE8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAyACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAMQA4AC4AMAAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBmAGYALQByAG8AYQBkACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACAAYQBuAGQAIABmAG8AcgBlAHMAdAByAHkAIABlAHEAdQBpAHAAbQBlAG4AdABcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAzACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAMQA3AC4AMwAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAATwBmAGYALQByAGEAZAAgAGUAcQB1AGkAcABtAGUAbgB0ACAAYQBuAGQAIAB2AGUAcwBzAGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABPAGYAZgAtAHIAbwBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAIABpAG4AIABvAGYAZgAtAHIAbwBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlACAAcQBcACIALAAgAFwAIgBFAEMAVAByAGEAbgBzACwAcQAgACgARwBKAC8AawBMACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEMATwAyACAARQBGAFQAcgBhAG4ALAAxACwAdABxAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABDAEgANAAgAEUARgBUAHIAYQBuACwAMQAsAHQAZwBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAATgAyAE8AIABFAEYAVAByAGEAbgAsADEALAB0AGcAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUARgBUAHIAYQBuAHMALAAzACwAcQAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIAUABlAHQAcgBvAGwAXAAiACwAIAAzADQALgAyACwAIAA2ADcALgA0ACwAIAAxADAALgAxACwAIAAwAC4AMwAsACAAMQA3AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIARgB1AGUAbAAgAE8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAANwAzAC4ANgAsACAAMAAuADIALAAgADAALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBmAGYALQByAG8AYQBkACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACAAYQBuAGQAIABmAG8AcgBlAHMAdAByAHkAIABlAHEAdQBpAHAAbQBlAG4AdABcACIALAAgAFwAIgBEAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgADYAOQAuADkALAAgADAALgAzACwAIAAwAC4ANQAsACAAMQA3AC4AMwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBGAHUAZQBsAF8ARwBlAHQAVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABTAHQAcgBpAG4AZwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALABcAG4AIAAgACAAIABMAEUARgBUACgAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsACAAXAAiACwAQwBlAGwAbAApACAALQAxACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAXABuACAAIAAgACAAUgBJAEcASABUACgAQwBlAGwAbAAsAEwARQBOACgAQwBlAGwAbAApAC0ARgBJAE4ARAAoAFwAIgAsACAAXAAiACwAQwBlAGwAbAApACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAFwAbgA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALAAgAEYAdQBlAGwAVQBzAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlACwAIABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFQAeQBwAGUALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAUwBVAE0AKABcAG4AIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAEYAdQBlAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACAAPQAgAEYAdQBlAGwAVAB5AHAAZQApACAAKgAgAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFUAcwBlACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgADAAXABuACAAIAApAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AOAA6ACAARgB1AGUAbAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgALgAxACAARgB1AGUAbAAgAFUAcwBlACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAAZgB1AGUAbABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRACwAIABFAEMALAAgAEUARgAsAFwAbgAgACAAIAAgACgAUQAgACoAIABFAEMAIAAqACAARQBGACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAbgBRACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAARwBKAC8AawBMAFwAbgBFAEYAIAA6ACAAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFQAcgBhAG4AcwB0AHEALAAgAEUAQwBfAFQAcgBhAG4AcwBxACwAIABFAEYAXwBUAHIAYQBuAHMAMQB0AHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAyAC4AMwAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB0ACAAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBxAFwAXABsAGUAZgB0ACgAUQBfAHsAVAByAGEAbgBzACwAdABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAVAByAGEAbgBzACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFQAcgBhAG4AcwAsADEALAB0AHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFQAcgBhAG4AcwB0AHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIABjAG8AbQBiAHUAcwB0AGUAZAAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIALAAgAFwAIgBWAGEAcgBpAGUAcwAgAGIAYQBzAGUAZAAgAG8AbgAgAGYAdQBlAGwAIAB0AHkAcABlADoAIABrAEwALAAgAG0AMwAsACAARwBKAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AVAByAGEAbgBzAHEAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AVAByAGEAbgBzADEAdABxAGcAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBcACIALAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAHUAcwBlAGQAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABrAEwAXABuAEUAQwAgADoAIABFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAIAA6ACAAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AUwBDAHEALAAgAEUAQwBfAFMAQwBxACwAIABFAEYAXwBTAEMAMQBxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA4AC4AMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADIAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcwBvAHUAcgBjAGUAcwAgAC0AIABDAGEAbABjAHUAbABhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFMAQwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUwBDACwAMQAsAHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AUwBDAHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFMAQwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AUwBDADEAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBxAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBDAFwAIgAsACAAXAAiAFMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADkAOgAgAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADkALgAxACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXABuAFQAaABlACAAdABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGkAbgBnACAAZAB1AHIAaQBuAGcAIABvAHAAZQByAGEAdABpAG8AbgAgACgAbgBvAHQAIABkAHUAcgBpAG4AZwAgAGkAbgBzAHQAYQBsAGwAYQB0AGkAbwBuACAAbwByACAAZABpAHMAcABvAHMAYQBsACkAXABuAEcAVwBQAFIAIAA6ACAARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSACAAOgAgAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAGMAaABhAHIAZwBlAF8AUgBhACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAGMAbwBuAHQAYQBpAG4AZQBkACAAaQBuACAAYQBwAHAAbABpAGEAbgBjAGUAIABhACAAOgAgAGsAZwBcAG4AbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAgADoAIABQAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAHQAbwB0AGEAbAAgAGMAaABhAHIAZwBlACAAbABlAGEAawBlAGQAIABmAHIAbwBtACAAYQBwAHAAbABpAGEAbgBjAGUAIABhACAAZQBhAGMAaAAgAHkAZQBhAHIAIAA6ACAAUABlAHIAYwBlAG4AdABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYwBoAGEAcgBnAGUAXwBSAGEALAAgAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALABcAG4AIAAgACAAIAAoAGMAaABhAHIAZwBlAF8AUgBhACAAKgAgACgAbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAvADEAMAAwACkAKQAgACoAIAAxADAAIABeACAALQAgADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AUgAsACAARwBXAFAAXwBSACwAXABuACAAIAAgACAAKAAoAEUAXwBSACAAKgAgADEAMABeADMAKQAgACoAIABHAFcAUABfAFIAKQAgACoAIAAxADAAXgAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABoAGUAIAB0AG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGwAZQBhAGsAaQBuAGcAIABkAHUAcgBpAG4AZwAgAG8AcABlAHIAYQB0AGkAbwBuACAAKABuAG8AdAAgAGQAdQByAGkAbgBnACAAaQBuAHMAdABhAGwAbABhAHQAaQBvAG4AIABvAHIAIABkAGkAcwBwAG8AcwBhAGwAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGwAZQBhAGsAYQBnAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAFIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAZwBhAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAzAC4AMQAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABpAG4AZAB1AHMAdAByAGkAYQBsACAAcAByAG8AYwBlAHMAcwBlAHMAIABlAG0AaQBzAHMAaQBvAG4AcwAgAC0AIABSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGEAZwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGMAaABhAHIAZwBlAF8AUgBhACAAKgAgACgAbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAvADEAMAAwACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBSACAAPQAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AYQAgAFwAXABsAGUAZgB0ACgAIABjAGgAYQByAGcAZQBfAHsAUgBhAH0AIABcAFwAdABpAG0AZQBzACAAXABcAGYAcgBhAGMAewBsAGUAYQBrAGEAZwBlAFwAXAAsAHIAYQB0AGUAXwBhAH0AewAxADAAMAB9ACAAXABcAHIAaQBnAGgAdAApACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMATwAyAGUAIAA9ACAAXABcAGwAZQBmAHQAKABFAF8AUgAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7ADMAfQAgAFwAXAByAGkAZwBoAHQAKQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAFIAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAaABhAHIAZwBlAF8AUgBhAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAGMAbwBuAHQAYQBpAG4AZQBkACAAaQBuACAAYQBwAHAAbABpAGEAbgBjAGUAIABhAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEAXAAiACwAIABcACIAUAByAGMAZQBuAHQAYQBnAGUAIABvAGYAIAB0AG8AdABhAGwAIABjAGgAYQByAGcAZQAgAGwAZQBhAGsAZQBkACAAZgByAG8AbQAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgAGUAYQBjAGgAIAB5AGUAYQByAFwAIgAsACAAXAAiAFAAZQByAGMAZQBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBhAFwAIgAsACAAXAAiAEEAcABwAGwAaQBhAG4AYwBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXAAiACwAIABcACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAF8AUgBcACIALAAgAFwAIgBUAG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAXAAiACwAIABcACIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGcAYQBzAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAOQAuADEALgAxACAAKAAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAF8AUgBcACIALAAgAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAXAAiACwAIABcACIARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABlAHEAdQBhAHQAaQBvAG4AIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAHQAbwAgAEMATwAyAC0AZQAgAHUAcwBpAG4AZwAgAHQAaABlACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0AFwAdQAwADAAMgA3AHMAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgACgARwBXAFAAKQAuAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEEAcABwAGUAbgBkAGkAeAAgADIAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzADoAIABUAGEAYgBsAGUAIAAyADMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsAHMAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABBAHAAcABlAG4AZABpAHgAIAAyACAALQAgAFQAYQBiAGwAZQAgADIAMwBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwA5ACwAIAA1ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAaABlAG0AaQBjAGEAbAAgAGYAbwByAG0AdQBsAGEAXAAiACwAIABcACIARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIAAoAEEAUgA1ACkAXAAiACwAIABcACIARwBhAHMAIAAtACAARgBDACAAbgBhAG0AZQBcACIALAAgAFwAIgBBAGQAaQB0AGkAbwBuAGEAbAAgAGQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAXAAiACwAIABcACIAQwBPADIAXAAiACwAIAAxACwAIABcACIAQwBPADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBDAEgANABcACIALAAgADIAOAAsACAAXAAiAEMASAA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAXAAiACwAIABcACIATgAyAE8AXAAiACwAIAAyADYANQAsACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBsAHAAaAB1AHIAIABoAGUAeABhAGYAbAB1AG8AcgBpAGQAZQBcACIALAAgAFwAIgBTAEYANgBcACIALAAgADIAMwA1ADAAMAAsACAAXAAiAFMARgA2AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgAzACAAKABSAC0AMgAzACkAXAAiACwAIABcACIAQwBIAEYAMwBcACIALAAgACAAMQAyADQAMAAwACwAIABcACIASABGAEMALQAyADMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAzADIAIAAoAFIALQAzADIAKQBcACIALAAgAFwAIgBDAEgAMgBGADIAXAAiACwAIAA2ADcANwAsACAAXAAiAEgARgBDAC0AMwAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0ANAAxACAAKABSAC0ANAAxACkAXAAiACwAIABcACIAQwBIADMARgBcACIALAAgACAAMQAxADYALAAgAFwAIgBIAEYAQwAtADQAMQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADQAMwAtADEAMABtAGUAZQAgACgAUgAtADQAMwAxADAAbQBlAGUAKQBcACIALAAgAFwAIgBDADUASAAyAEYAMQAwAFwAIgAsACAAMQA2ADUAMAAsACAAXAAiAEgARgBDAC0ANAAzAC0AMQAwAG0AZQBlAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQAyADUAIAAoAFIALQAxADIANQApAFwAIgAsACAAXAAiAEMAMgBIAEYANQBcACIALAAgACAAMwAxADcAMAAsACAAXAAiAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADMANAAgACgAUgAtADEAMwA0ACkAXAAiACwAIABcACIAQwAyAEgAMgBGADQAIAAoAEMASABGADIAQwBIAEYAMgApAFwAIgAsACAAIAAxADEAMgAwACwAIABcACIASABGAEMALQAxADMANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEAMwA0AGEAIAAoAFIALQAxADMANABhACkAXAAiACwAIABcACIAQwAyAEgAMgBGADQAIAAoAEMASAAyAEYAQwBGADMAKQBcACIALAAgADEAMwAwADAALAAgAFwAIgBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADQAMwAgACgAUgAtADEANAAzACkAXAAiACwAIABcACIAQwAyAEgAMwBGADMAIAAoAEMASABGADIAQwBIADIARgApAFwAIgAsACAAMwAyADgALAAgAFwAIgBIAEYAQwAtADEANAAzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA0ADMAYQAgACgAUgAtADEANAAzAGEAKQBcACIALAAgAFwAIgBDADIASAAzAEYAMwAgACgAQwBGADMAQwBIADMAKQBcACIALAAgADQAOAAwADAALAAgAFwAIgBIAEYAQwAtADEANAAzAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADUAMgBhACAAKABSAC0AMQA1ADIAYQApAFwAIgAsACAAXAAiAEMAMgBIADQARgAyACAAKABDAEgAMwBDAEgARgAyACkAXAAiACwAIAAxADMAOAAsACAAXAAiAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMgA3AGUAYQAgACgAUgAtADIAMgA3AGUAYQApAFwAIgAsACAAXAAiAEMAMwBIAEYANwBcACIALAAgADMAMwA1ADAALAAgAFwAIgBIAEYAQwAtADIAMgA3AGUAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMwA2AGYAYQAgACgAUgAtADIAMwA2AGYAYQApAFwAIgAsACAAXAAiAEMAMwBIADIARgA2AFwAIgAsACAAOAAwADYAMAAsACAAXAAiAEgARgBDAC0AMgAzADYAZgBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgA0ADUAYwBhACAAKABSAC0AMgA0ADUAYwBhACkAXAAiACwAIABcACIAQwAzAEgAMwBGADUAXAAiACwAIAA3ADEANgAsACAAXAAiAEgARgBDAC0AMgA0ADUAYwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgA0ADUAZgBhACAAKABSAC0AMgA0ADUAZgBhACkAXAAiACwAIABcACIAQwBIAEYAMgBDAEgAMgBDAEYAMwBcACIALAAgADgANQA4ACwAIABcACIASABGAEMALQAyADQANQBmAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAzADYANQBtAGYAYwAgACgAUgAtADMANgA1AG0AZgBjACkAXAAiACwAIABcACIAQwBIADMAQwBGADIAQwBIADIAQwBGADMAXAAiACwAIAA4ADAANAAsACAAXAAiAEgARgBDAC0AMwA2ADUAbQBmAGMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADIAMgAgACgAUgAtADIAMgApAFwAIgAsACAAXAAiAEMASABDAGwARgAyAFwAIgAsACAAMQA3ADYAMAAsACAAXAAiAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEAMgAzACAAKABSAC0AMQAyADMAKQBcACIALAAgAFwAIgBDAEgAQwBsADIAMgBDAEYAMwBcACIALAAgADcAOQAsACAAXAAiAEgAQwBGAEMALQAxADIAMwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQAyADQAIAAoAFIALQAxADIANAApAFwAIgAsACAAXAAiAEMASABDAGwARgBDAEYAMwBcACIALAAgADUAMgA3ACwAIABcACIASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADQAMQBiACAAKABSAC0AMQA0ADEAYgApAFwAIgAsACAAXAAiAEMASAAzAEMAQwBsADIARgBcACIALAAgADcAOAAyACwAIABcACIASABDAEYAQwAtADEANAAxAGIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEANAAyAGIAIAAoAFIALQAxADQAMgBiACkAXAAiACwAIABcACIAQwBIADIAQwBDAGwARgAyAFwAIgAsACAAMQA5ADgAMAAsACAAXAAiAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGEAIAAoAFIALQAyADIANQBjAGEAKQBcACIALAAgAFwAIgBDAEgAQwBsADIAQwBGADIAQwBGADMAXAAiACwAIAAxADIANwAsACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADIAMgA1AGMAYgAgACgAUgAtADIAMgA1AGMAYgApAFwAIgAsACAAXAAiAEMASABDAGwARgBDAEYAMgBDAEMASQBGADIAXAAiACwAIAA1ADIANQAsACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAxADQAIABQAGUAcgBmAGwAdQBvAHIAbwBtAGUAdABoAGEAbgBlACAAKAB0AGUAdAByAGEAZgBsAHUAbwByAG8AbQBlAHQAaABhAG4AZQApAFwAIgAsACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAAsACAAXAAiAFAARgBDAC0AMQA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMQAxADYAIABQAGUAcgBmAGwAdQBvAHIAbwBlAHQAaABhAG4AZQAgACgAaABlAHgAYQBmAGwAdQBvAHIAbwBlAHQAaABhAG4AZQApAFwAIgAsACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADEAMQAwADAALAAgAFwAIgBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMgAxADgAIABQAGUAcgBmAGwAdQBvAHIAbwBwAHIAbwBwAGEAbgBlAFwAIgAsACAAXAAiAEMAMwBGADgAXAAiACwAIAA4ADkAMAAwACwAIABcACIAUABGAEMALQAyADEAOABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADMAMQAtADEAMAAgAFAAZQByAGYAbAB1AG8AcgBvAGIAdQB0AGEAbgBlAFwAIgAsACAAXAAiAEMANABGADEAMABcACIALAAgADkAMgAwADAALAAgAFwAIgBQAEYAQwAtADMAMQAtADEAMABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADMAMQA4ACAAUABlAHIAZgBsAHUAbwByAG8AYwB5AGMAbABvAGIAdQB0AGEAbgBlAFwAIgAsACAAXAAiAGMALQBDADQARgA4AFwAIgAsACAAOQA1ADQAMAAsACAAXAAiAFAARgBDAC0AMwAxADgAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA0ADEALQAxADIAIABQAGUAcgBmAGwAdQBvAHIAbwBwAGUAbgB0AGEAbgBlAFwAIgAsACAAXAAiAEMANQBGADEAMgBcACIALAAgADgANQA1ADAALAAgAFwAIgBQAEYAQwAtADQAMQAtADEAMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADUAMQAtADEANAAgAFAAZQByAGYAbAB1AG8AcgBvAGgAZQB4AGEAbgBlAFwAIgAsACAAXAAiAEMANgBGADEANABcACIALAAgADcAOQAxADAALAAgAFwAIgBQAEYAQwAtADUAMQAtADEANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADkAMQAtADEAOAAgAFAAZQByAGYAbAB1AG4AYQBmAGUAbgBlAFwAIgAsACAAXAAiAEMAMQAwAEYAMQA4AFwAIgAsACAANwAxADkAMAAsACAAXAAiAFAARgBDAC0AOQAxAC0AMQA4AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAyAFwAIgAsACAAXAAiAEMAQwBsADIARgAyAFwAIgAsACAAMQAwADIAMAAwACwAIABcACIAQwBGAEMALQAxADIAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMwBcACIALAAgAFwAIgBDAEMAbABGADMAXAAiACwAIAAxADMAOQAwADAALAAgAFwAIgBDAEYAQwAtADEAMwBcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAQwBDAGwARgAyAEMAQwBsAEYAMgBcACIALAAgADgANQA5ADAALAAgAFwAIgBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADEANQBcACIALAAgAFwAIgBDAEMAbABGADIAQwBGADMAXAAiACwAIAA3ADYANwAwACwAIABcACIAQwBGAEMALQAxADEANQBcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBHAEEAUwAgAC0AIABGAEMAIABuAGEAbQBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAdAByAHUAbgBjAGEAdABlAGQAIABnAGEAcwAgAG4AYQBtAGUAIAB0AG8AIABhAGwAbABvAHcAIABtAGEAdABjAGgAaQBuAGcAIAB3AGkAdABoACAAbwB0AGgAZQByACAAdABhAGIAbABlAHMALgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAGcAYQBzAGUAcwAgAGYAcgBvAG0AIABJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBBAGQAZABpAHQAaQBvAG4AYQBsACAAZABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4ALgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEEAcABwAGUAbgBkAGkAeAAgADIAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzADoAIABCAGwAZQBuAGQAZQBkACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQgBsAGUAbgBkAGUAZAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABzACAAKABtAGEAbgB5ACAAYwBvAG4AdABhAGkAbgBpAG4AZwAgAEgARgBDAFMAIABhAG4AZAAvAG8AcgAgAFAARgBDAFMAKQBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAEEAcABwAGUAbgBkAGkAeAAgADIAIAAtACAAVABhAGIAbABlACAAMgA0AFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ADEALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBsAGUAbgBkAFwAIgAsACAAXAAiAEMAbwBuAHMAdABpAHQAdQBlAG4AdABzAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAGkAdABpAG8AbgAgACgAJQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMABcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAUgAtADQAMAAwACAAYwBhAG4AIABoAGEAdgBlACAAdgBhAHIAaQBvAHUAcwAgAHAAcgBvAHAAbwByAHQAaQBvAG4AcwAgAG8AZgAgAEMARgBDAC0AMQAyACAAYQBuAGQAIABDAEYAQwAtADEAMQA0AC4AIABUAGgAZQAgAGUAeABhAGMAdAAgAGMAbwBtAHAAbwBzAGkAdABpAG8AbgAgAG4AZQBlAGQAcwAgAHQAbwAgAGIAZQAgAHMAcABlAGMAaQBmAGkAZQBkACwAIABlAC4AZwAuACwAIABSAC0ANAAwADAAIAAoADYAMAAvADQAMAApAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAxAEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgAoADUAMwAuADAALwAxADMALgAwAC8AMwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMQBCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAKAA2ADEALgAwAC8AMQAxAC4AMAAvADIAOAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADEAQwBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiACgAMwAzAC4AMAAvADEANQAuADAALwA1ADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAyAEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADYAMAAuADAALwAyAC4AMAAvADMAOAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADIAQgBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABDAC0AMgA5ADAALwBIAEMARgBDAC0AMgAyAFwAIgAsACAAXAAiACgAMwA4AC4AMAAvADIALgAwAC8ANgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMwBBAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAKAA1AC4AMAAvADcANQAuADAALwAyADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAzAEIAXAAiACwAIABcACIASABDAC0AMgA5ADAALwBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOABcACIALAAgAFwAIgAoADUALgAwAC8ANQA2AC4AMAAvADMAOQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADQAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADQAMwBhAC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgANAA0AC4AMAAvADUAMgAuADAALwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwAgAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADQAMgBiAC8AUABGAEMALQAzADEAOABcACIALAAgAFwAIgAoADQANQAuADAALwA3AC4AMAAvADUALgA1AC8ANAAyAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANgBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEMALQA2ADAAMABhAC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA1ADUALgAwAC8AMQA0AC4AMAAvADQAMQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcAQQBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAyADAALgAwAC8ANAAwAC4AMAAvADQAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcAQgBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAxADAALgAwAC8ANwAwAC4AMAAvADIAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcAQwBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAyADMALgAwAC8AMgA1AC4AMAAvADUAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcARABcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAxADUALgAwAC8AMQA1AC4AMAAvADcAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcARQBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAyADUALgAwAC8AMQA1AC4AMAAvADYAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADgAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADQAMwBhAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADcALgAwAC8ANAA2AC4AMAAvADQANwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADkAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA2ADAALgAwAC8AMgA1AC4AMAAvADEANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADkAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA2ADUALgAwAC8AMgA1AC4AMAAvADEAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADAAQQBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAKAA1ADAALgAwAC8ANQAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMABCAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQBcACIALAAgAFwAIgAoADQANQAuADAALwA1ADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAxAEEAXAAiACwAIABcACIASABDAC0AMQAyADcAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAxAC4ANQAvADgANwAuADUALwAxADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAxAEIAXAAiACwAIABcACIASABDAC0AMQAyADcAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAzAC4AMAAvADkANAAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBDAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMwAuADAALwA5ADUALgA1AC8AMQAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADIAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANwAwAC4AMAAvADUALgAwAC8AMgA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMwBBAFwAIgAsACAAXAAiAFAARgBDAC0AMgAxADgALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgAOQAuADAALwA4ADgALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADQAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQAxAC4AMAAvADIAOAAuADUALwA0AC4AMAAvADEANgAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADQAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQAwAC4AMAAvADMAOQAuADAALwAxAC4ANQAvADkALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA1AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADgAMgAuADAALwAxADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA1AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADIANQAuADAALwA3ADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA2AEEAXAAiACwAIABcACIASABGAEMALQAxADMANABhAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAC0ANgAwADAAXAAiACwAIABcACIAKAA1ADkALgAwAC8AMwA5AC4ANQAvADEALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA3AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQAvAEgAQwAtADYAMAAwAFwAIgAsACAAXAAiACgANAA2AC4ANgAvADUAMAAuADAALwAzAC4ANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAOABBAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADEALgA1AC8AOQA2AC4AMAAvADIALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA5AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQAvAEgARQAtAEUAMQA3ADAAXAAiACwAIABcACIAKAA3ADcALgAwAC8AMQA5AC4AMAAvADQALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMgAwAEEAXAAiACwAIABcACIASABGAEMALQAxADMANABhAC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA4ADgALgAwAC8AMQAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMQBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAA1ADgALgAwAC8ANAAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgAOAA1AC4AMQAvADEAMQAuADUALwAzAC4ANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMgBCAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgANQA1AC4AMAAvADQAMgAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMgBDAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgAOAAyAC4AMAAvADEANQAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMABcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADcAMwAuADgALwAyADYALgAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAxAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBDAEYAQwAtADEAMgBcACIALAAgAFwAIgAoADcANQAuADAALwAyADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAyAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBDAEYAQwAtADEAMQA1AFwAIgAsACAAXAAiACgANAA4AC4AOAAvADUAMQAuADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADMAXAAiACwAIABcACIASABGAEMALQAyADMALwBDAEYAQwAtADEAMwBcACIALAAgAFwAIgAoADQAMAAuADEALwA1ADkALgA5ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA0AFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8AQwBGAEMALQAxADEANQBcACIALAAgAFwAIgAoADQAOAAuADIALwA1ADEALgA4ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA1AFwAIgAsACAAXAAiAEMARgBDAC0AMQAyAC8ASABDAEYAQwAtADMAMQBcACIALAAgAFwAIgAoADcAOAAuADAALwAyADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA2AFwAIgAsACAAXAAiAEMARgBDAC0AMwAxAC8AQwBGAEMALQAxADEANABcACIALAAgAFwAIgAoADUANQAuADEALwA0ADQALgA5ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA3AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQBcACIALAAgAFwAIgAoADUAMAAuADAALwA1ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA4AEEAXAAiACwAIABcACIASABGAEMALQAyADMALwBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiACgAMwA5AC4AMAAvADYAMQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADgAQgBcACIALAAgAFwAIgBIAEYAQwAtADIAMwAvAFAARgBDAC0AMQAxADYAXAAiACwAIABcACIAKAA0ADYALgAwAC8ANQA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAOQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiACgANAA0AC4AMAAvADUANgAuADAAKQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABjAGgAYQBuAGcAZQBkACAASABDADYAMAAwAGEAIAB0AG8AIABIAEMALQA2ADAAMABhACAAZgBvAHIAIABiAGwAZQBuAGQAIABSAC0ANAAxADQAQgAuACAARgBpAHgAZQBkACAAdAB5AHAAbwAgAGYAbwByACAAYgBsAGUAbgBkACAAUgAtADQAMAA1AEEAIAAtACAAQwBoAGEAbgBnAGUAZAAgAEgAQwBGAEMAMQA0ADIAYgAgAHQAbwAgAEgAQwBGAEMALQAxADQAMgBiAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ATABlAGEAawBhAGcAZQAgAHIAYQB0AGUAcwAgAGYAbwByACAAYwBvAG0AbQBvAG4AIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuACAAYQBuAGQAIABhAGkAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEkAbgBkAGkAYwBhAHQAaQB2AGUAIABsAGUAYQBrAGEAZwBlACAAcgBhAHQAZQBzACAAZgBvAHIAIABjAG8AbQBtAG8AbgAgAHIAZQBmAHIAaQBnAGUAcgBhAHQAaQBvAG4AIABhAG4AZAAgAGEAaQByACAALQAgAGMAbwBuAGQAaQB0AGkAbwBuAGkAbgBnACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAMQAwAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAGwAZQBhAGsAYQBnAGUAIAByAGEAdABlACAAKAAlACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAcgBlAGYAcgBpAGcAZQByAGEAdABvAHIAcwBcACIALAAgADEALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuAFwAIgAsACAAMQA1AC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAEEALwBDACAAcABvAHIAdABhAGIAbABlAFwAIgAsACAAMgAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIABBAC8AQwAgAHMAcABsAGkAdABcACIALAAgADMALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAQQAvAEMAIABwAGEAYwBrAGEAZwBlAGQAXAAiACwAIAAyAC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAHYAZQBoAGkAYwBsAGUAIABBAC8AQwBcACIALAAgADYALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAdgBlAGgAaQBjAGwAZQAgAEEALwBDAFwAIgAsACAAMQAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBhAGwAYwB1AGwAYQB0AGUAQgBsAGUAbgBkAEcAVwBQAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMQAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMgAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMwAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAANAAsAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAxACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAyACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAzACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAA0ACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVQBuAGkAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVABpAHQAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFUAbgBpAHQAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVABpAHQAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGEAdABhACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAYQBsAGMAdQBsAGEAdABlAEIAbABlAG4AZABHAFcAUAAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20041,18 +20046,13 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/9_Refrigerants_WIP_v02.xlsx
+++ b/Excel/9_Refrigerants_WIP_v02.xlsx
@@ -840,9 +840,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF183C1B"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>R</t>
@@ -859,9 +859,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF183C1B"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Ra</t>
@@ -878,9 +878,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF183C1B"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>CO2-e</t>
@@ -906,9 +906,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="16"/>
+        <sz val="14"/>
         <color theme="1" tint="0.24994659260841701"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>CO2e</t>
@@ -1118,108 +1118,106 @@
   </numFmts>
   <fonts count="53" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF533001"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
@@ -1230,249 +1228,243 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFC44340"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1" tint="0.14996795556505021"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC44340"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <color theme="0"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
       <sz val="12"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color theme="6" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color theme="5" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <vertAlign val="subscript"/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="1" tint="0.14999847407452621"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3" tint="9.9978637043366805E-2"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="subscript"/>
+      <sz val="14"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="3" tint="9.9978637043366805E-2"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="16"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <vertAlign val="subscript"/>
-      <sz val="16"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF404040"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="16">
@@ -2384,11 +2376,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2408,11 +2399,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2432,11 +2422,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2456,11 +2445,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2480,11 +2468,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2504,11 +2491,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2528,11 +2514,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2552,11 +2537,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2576,11 +2560,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2600,11 +2583,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2624,11 +2606,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2648,11 +2629,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2672,11 +2652,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2696,11 +2675,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2720,11 +2698,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2744,11 +2721,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2768,11 +2744,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2792,11 +2767,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2816,11 +2790,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2840,11 +2813,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2864,11 +2836,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2888,11 +2859,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2912,11 +2882,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2936,11 +2905,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2960,11 +2928,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2984,11 +2951,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3008,11 +2974,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3032,11 +2997,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3056,11 +3020,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3080,11 +3043,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3104,11 +3066,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3128,11 +3089,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3152,11 +3112,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3176,11 +3135,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3200,11 +3158,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3224,11 +3181,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3248,11 +3204,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3558,7 +3513,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-AU" sz="1400" b="0">
+            <a:rPr lang="en-AU" sz="1200" b="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -3566,14 +3521,14 @@
             <a:t>9.1.1.1-2 </a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-AU" sz="1400" b="0">
+            <a:rPr lang="en-AU" sz="1200" b="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="en-AU" sz="1400" b="0">
+            <a:rPr lang="en-AU" sz="1200" b="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -3581,14 +3536,14 @@
             <a:t>Refrigerant</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-AU" sz="1400" b="0" baseline="0">
+            <a:rPr lang="en-AU" sz="1200" b="0" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
             </a:rPr>
             <a:t> use</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1400" b="0">
+          <a:endParaRPr lang="en-AU" sz="1200" b="0">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -3660,17 +3615,17 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:fld id="{B377A225-5B38-4F4F-8E60-34C9F7D0C552}" type="TxLink">
-            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>The total emissions of refrigerant leaking during operation (not during installation or disposal)</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="1000">
+          <a:endParaRPr lang="en-AU" sz="900">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -3743,14 +3698,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐸</m:t>
@@ -3758,13 +3713,13 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐶𝐻</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>4</m:t>
@@ -3772,7 +3727,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=</m:t>
@@ -3782,14 +3737,14 @@
                         <m:chr m:val="∑"/>
                         <m:supHide m:val="on"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:naryPr>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑗</m:t>
@@ -3802,14 +3757,14 @@
                             <m:chr m:val="∑"/>
                             <m:supHide m:val="on"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:naryPr>
                           <m:sub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑘</m:t>
@@ -3822,14 +3777,14 @@
                                 <m:chr m:val="∑"/>
                                 <m:supHide m:val="on"/>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:naryPr>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑚</m:t>
@@ -3842,14 +3797,14 @@
                                     <m:chr m:val="∑"/>
                                     <m:supHide m:val="on"/>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:naryPr>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑇</m:t>
@@ -3860,7 +3815,7 @@
                                     <m:d>
                                       <m:dPr>
                                         <m:ctrlPr>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                         </m:ctrlPr>
@@ -3869,14 +3824,14 @@
                                         <m:sSub>
                                           <m:sSubPr>
                                             <m:ctrlPr>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                             </m:ctrlPr>
                                           </m:sSubPr>
                                           <m:e>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝐷</m:t>
@@ -3884,7 +3839,7 @@
                                           </m:e>
                                           <m:sub>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑗𝑘</m:t>
@@ -3892,7 +3847,7 @@
                                           </m:sub>
                                         </m:sSub>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>×</m:t>
@@ -3900,14 +3855,14 @@
                                         <m:sSub>
                                           <m:sSubPr>
                                             <m:ctrlPr>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                             </m:ctrlPr>
                                           </m:sSubPr>
                                           <m:e>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑀</m:t>
@@ -3915,7 +3870,7 @@
                                           </m:e>
                                           <m:sub>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑗𝑘𝑚𝑇</m:t>
@@ -3923,7 +3878,7 @@
                                           </m:sub>
                                         </m:sSub>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>×</m:t>
@@ -3931,14 +3886,14 @@
                                         <m:sSub>
                                           <m:sSubPr>
                                             <m:ctrlPr>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                             </m:ctrlPr>
                                           </m:sSubPr>
                                           <m:e>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑁</m:t>
@@ -3946,7 +3901,7 @@
                                           </m:e>
                                           <m:sub>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑗𝑘</m:t>
@@ -3964,7 +3919,7 @@
                       </m:e>
                     </m:nary>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
@@ -3972,14 +3927,14 @@
                     <m:sSup>
                       <m:sSupPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSupPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>10</m:t>
@@ -3987,7 +3942,7 @@
                       </m:e>
                       <m:sup>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>−3</m:t>
@@ -3997,7 +3952,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -4045,12 +4000,12 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝐸_𝐶𝐻4=∑8_𝑗▒∑8_𝑘▒∑8_𝑚▒∑8_𝑇▒(𝐷_𝑗𝑘×𝑀_𝑗𝑘𝑚𝑇×𝑁_𝑗𝑘 ) ×10^(−3)</a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -4132,7 +4087,7 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:solidFill>
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
@@ -4145,7 +4100,7 @@
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:solidFill>
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
@@ -4159,7 +4114,7 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:solidFill>
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
@@ -4173,7 +4128,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:solidFill>
                           <a:schemeClr val="tx1"/>
                         </a:solidFill>
@@ -4190,7 +4145,7 @@
                         <m:limLoc m:val="subSup"/>
                         <m:supHide m:val="on"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:solidFill>
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
@@ -4203,7 +4158,7 @@
                       </m:naryPr>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:solidFill>
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
@@ -4220,7 +4175,7 @@
                         <m:d>
                           <m:dPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:solidFill>
                                   <a:schemeClr val="tx1"/>
                                 </a:solidFill>
@@ -4233,7 +4188,7 @@
                           </m:dPr>
                           <m:e>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:solidFill>
                                   <a:schemeClr val="tx1"/>
                                 </a:solidFill>
@@ -4247,7 +4202,7 @@
                             <m:sSub>
                               <m:sSubPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:solidFill>
                                       <a:schemeClr val="tx1"/>
                                     </a:solidFill>
@@ -4260,7 +4215,7 @@
                               </m:sSubPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:solidFill>
                                       <a:schemeClr val="tx1"/>
                                     </a:solidFill>
@@ -4274,7 +4229,7 @@
                               </m:e>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:solidFill>
                                       <a:schemeClr val="tx1"/>
                                     </a:solidFill>
@@ -4288,7 +4243,7 @@
                               </m:sub>
                             </m:sSub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:solidFill>
                                   <a:schemeClr val="tx1"/>
                                 </a:solidFill>
@@ -4302,7 +4257,7 @@
                             <m:f>
                               <m:fPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:solidFill>
                                       <a:schemeClr val="tx1"/>
                                     </a:solidFill>
@@ -4315,7 +4270,7 @@
                               </m:fPr>
                               <m:num>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:solidFill>
                                       <a:schemeClr val="tx1"/>
                                     </a:solidFill>
@@ -4327,7 +4282,7 @@
                                   <m:t>𝑙𝑒𝑎𝑘𝑎𝑔𝑒</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:solidFill>
                                       <a:schemeClr val="tx1"/>
                                     </a:solidFill>
@@ -4339,7 +4294,7 @@
                                   <m:t> </m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:solidFill>
                                       <a:schemeClr val="tx1"/>
                                     </a:solidFill>
@@ -4353,7 +4308,7 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:solidFill>
                                           <a:schemeClr val="tx1"/>
                                         </a:solidFill>
@@ -4366,7 +4321,7 @@
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:solidFill>
                                           <a:schemeClr val="tx1"/>
                                         </a:solidFill>
@@ -4380,7 +4335,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:solidFill>
                                           <a:schemeClr val="tx1"/>
                                         </a:solidFill>
@@ -4396,7 +4351,7 @@
                               </m:num>
                               <m:den>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:solidFill>
                                       <a:schemeClr val="tx1"/>
                                     </a:solidFill>
@@ -4414,7 +4369,7 @@
                       </m:e>
                     </m:nary>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:solidFill>
                           <a:schemeClr val="tx1"/>
                         </a:solidFill>
@@ -4428,7 +4383,7 @@
                     <m:sSup>
                       <m:sSupPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:solidFill>
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
@@ -4441,7 +4396,7 @@
                       </m:sSupPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:solidFill>
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
@@ -4455,7 +4410,7 @@
                       </m:e>
                       <m:sup>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:solidFill>
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
@@ -4471,7 +4426,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -4536,7 +4491,7 @@
                 <a:defRPr/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
@@ -4547,7 +4502,7 @@
                 </a:rPr>
                 <a:t>𝐸_𝑅=∑10_𝑎▒(𝑐ℎ𝑎𝑟𝑔𝑒_𝑅𝑎×(𝑙𝑒𝑎𝑘𝑎𝑔𝑒 𝑟𝑎𝑡𝑒_𝑎)/100) ×10^(−3)</a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -4613,14 +4568,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐸</m:t>
@@ -4628,7 +4583,7 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐶</m:t>
@@ -4636,25 +4591,25 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>𝑂</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>2</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>𝑒</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=</m:t>
@@ -4662,7 +4617,7 @@
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -4671,14 +4626,14 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:sSubPr>
                           <m:e>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝐸</m:t>
@@ -4686,7 +4641,7 @@
                           </m:e>
                           <m:sub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑅</m:t>
@@ -4694,7 +4649,7 @@
                           </m:sub>
                         </m:sSub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>×</m:t>
@@ -4702,14 +4657,14 @@
                         <m:sSup>
                           <m:sSupPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:sSupPr>
                           <m:e>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>10</m:t>
@@ -4717,7 +4672,7 @@
                           </m:e>
                           <m:sup>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>3</m:t>
@@ -4727,13 +4682,13 @@
                       </m:e>
                     </m:d>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>𝐺𝑊</m:t>
@@ -4741,14 +4696,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑃</m:t>
@@ -4756,7 +4711,7 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑅</m:t>
@@ -4764,7 +4719,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
@@ -4772,14 +4727,14 @@
                     <m:sSup>
                       <m:sSupPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSupPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>10</m:t>
@@ -4787,7 +4742,7 @@
                       </m:e>
                       <m:sup>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>−3</m:t>
@@ -4797,7 +4752,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -4845,12 +4800,12 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝐸_𝐶 𝑂2𝑒=(𝐸_𝑅×10^3 )×𝐺𝑊𝑃_𝑅×10^(−3)</a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -5632,12 +5587,12 @@
     </a:clrScheme>
     <a:fontScheme name="Custom 1">
       <a:majorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -5848,31 +5803,31 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A3" s="79" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A6" s="78" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A7" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A8" s="12" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -5889,7 +5844,7 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:W45"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -5919,7 +5874,7 @@
       <c r="O1" s="56"/>
       <c r="P1" s="56"/>
     </row>
-    <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="56"/>
       <c r="D2" s="56"/>
       <c r="E2" s="56"/>
@@ -5936,7 +5891,7 @@
       <c r="P2" s="56"/>
       <c r="Q2" s="57"/>
     </row>
-    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -5956,13 +5911,13 @@
       <c r="O3" s="58"/>
       <c r="P3" s="58"/>
     </row>
-    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="44" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -5982,7 +5937,7 @@
       <c r="N5" s="34"/>
       <c r="O5" s="31"/>
     </row>
-    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="59" t="s">
         <v>84</v>
       </c>
@@ -5998,83 +5953,83 @@
       <c r="N6" s="33"/>
       <c r="O6" s="32"/>
     </row>
-    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - Refrigerants'!A1", "Refrigerants")</f>
         <v>Refrigerants</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'9.1.1.1-2 Refrigerant use'!A1", "9.1.1.1-2 Refrigerant use")</f>
         <v>9.1.1.1-2 Refrigerant use</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O14" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="str">
         <f>HYPERLINK("#'Constants - Refrigerants'!A1", "Constants - Refrigerants")</f>
         <v>Constants - Refrigerants</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L37" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="12:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="12:23" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="W45" t="s">
         <v>82</v>
       </c>
@@ -6092,7 +6047,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:K87"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="3" width="2.7109375" customWidth="1"/>
@@ -6110,10 +6065,10 @@
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="8"/>
     </row>
-    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -6128,7 +6083,7 @@
       <c r="J3" s="15"/>
       <c r="K3" s="15"/>
     </row>
-    <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
@@ -6145,7 +6100,7 @@
       <c r="J4" s="16"/>
       <c r="K4" s="17"/>
     </row>
-    <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -6160,7 +6115,7 @@
       <c r="J5" s="19"/>
       <c r="K5" s="15"/>
     </row>
-    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="15"/>
       <c r="D6" s="62" t="s">
         <v>80</v>
@@ -6173,7 +6128,7 @@
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
     </row>
-    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -6184,7 +6139,7 @@
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
     </row>
-    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
@@ -6210,7 +6165,7 @@
       <c r="J8" s="40"/>
       <c r="K8" s="15"/>
     </row>
-    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - Refrigerants'!A1", "Refrigerants")</f>
         <v>Refrigerants</v>
@@ -6245,7 +6200,7 @@
       </c>
       <c r="K9" s="15"/>
     </row>
-    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="15"/>
       <c r="D10" s="1"/>
       <c r="E10" s="54">
@@ -6274,7 +6229,7 @@
       </c>
       <c r="K10" s="15"/>
     </row>
-    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="15"/>
       <c r="D11" s="1"/>
       <c r="E11" s="54">
@@ -6303,7 +6258,7 @@
       </c>
       <c r="K11" s="15"/>
     </row>
-    <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
@@ -6335,7 +6290,7 @@
       </c>
       <c r="K12" s="15"/>
     </row>
-    <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'9.1.1.1-2 Refrigerant use'!A1", "9.1.1.1-2 Refrigerant use")</f>
         <v>9.1.1.1-2 Refrigerant use</v>
@@ -6368,7 +6323,7 @@
       </c>
       <c r="K13" s="15"/>
     </row>
-    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="15"/>
       <c r="D14" s="1"/>
       <c r="E14" s="54">
@@ -6397,7 +6352,7 @@
       </c>
       <c r="K14" s="15"/>
     </row>
-    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="15"/>
       <c r="D15" s="1"/>
       <c r="E15" s="54">
@@ -6426,7 +6381,7 @@
       </c>
       <c r="K15" s="15"/>
     </row>
-    <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78" t="s">
         <v>1</v>
       </c>
@@ -6458,7 +6413,7 @@
       </c>
       <c r="K16" s="15"/>
     </row>
-    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="str">
         <f>HYPERLINK("#'Constants - Refrigerants'!A1", "Constants - Refrigerants")</f>
         <v>Constants - Refrigerants</v>
@@ -6491,7 +6446,7 @@
       </c>
       <c r="K17" s="15"/>
     </row>
-    <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -6524,7 +6479,7 @@
       </c>
       <c r="K18" s="15"/>
     </row>
-    <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="15"/>
       <c r="D19" s="21" t="s">
         <v>54</v>
@@ -6545,7 +6500,7 @@
       </c>
       <c r="K19" s="15"/>
     </row>
-    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="15"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -6556,7 +6511,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="15"/>
     </row>
-    <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="15"/>
       <c r="D21" s="1"/>
       <c r="E21" s="41"/>
@@ -6567,7 +6522,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="15"/>
     </row>
-    <row r="22" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="15"/>
       <c r="D22" s="1"/>
       <c r="E22" s="41"/>
@@ -6578,7 +6533,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="15"/>
     </row>
-    <row r="23" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="15"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -6589,7 +6544,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="15"/>
     </row>
-    <row r="24" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="15"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -6600,7 +6555,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="15"/>
     </row>
-    <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="15"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -6611,7 +6566,7 @@
       <c r="J25" s="1"/>
       <c r="K25" s="15"/>
     </row>
-    <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="15"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -6622,7 +6577,7 @@
       <c r="J26" s="1"/>
       <c r="K26" s="15"/>
     </row>
-    <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="15"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -6633,7 +6588,7 @@
       <c r="J27" s="1"/>
       <c r="K27" s="15"/>
     </row>
-    <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="15"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -6644,7 +6599,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="15"/>
     </row>
-    <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="15"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -6655,7 +6610,7 @@
       <c r="J29" s="1"/>
       <c r="K29" s="15"/>
     </row>
-    <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="15"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -6666,7 +6621,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="15"/>
     </row>
-    <row r="31" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="15"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -6677,7 +6632,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="15"/>
     </row>
-    <row r="32" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="15"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -6688,7 +6643,7 @@
       <c r="J32" s="1"/>
       <c r="K32" s="15"/>
     </row>
-    <row r="33" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="15"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -6699,7 +6654,7 @@
       <c r="J33" s="1"/>
       <c r="K33" s="15"/>
     </row>
-    <row r="34" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="15"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -6710,7 +6665,7 @@
       <c r="J34" s="1"/>
       <c r="K34" s="15"/>
     </row>
-    <row r="35" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="15"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -6721,7 +6676,7 @@
       <c r="J35" s="1"/>
       <c r="K35" s="15"/>
     </row>
-    <row r="36" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="15"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -6732,7 +6687,7 @@
       <c r="J36" s="1"/>
       <c r="K36" s="15"/>
     </row>
-    <row r="37" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="15"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -6743,7 +6698,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="15"/>
     </row>
-    <row r="38" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="15"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -6754,7 +6709,7 @@
       <c r="J38" s="1"/>
       <c r="K38" s="15"/>
     </row>
-    <row r="39" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="15"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -6765,7 +6720,7 @@
       <c r="J39" s="1"/>
       <c r="K39" s="15"/>
     </row>
-    <row r="40" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="15"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -6776,7 +6731,7 @@
       <c r="J40" s="1"/>
       <c r="K40" s="15"/>
     </row>
-    <row r="41" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="15"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -6787,7 +6742,7 @@
       <c r="J41" s="1"/>
       <c r="K41" s="15"/>
     </row>
-    <row r="42" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="15"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -6798,7 +6753,7 @@
       <c r="J42" s="1"/>
       <c r="K42" s="15"/>
     </row>
-    <row r="43" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="15"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -6809,7 +6764,7 @@
       <c r="J43" s="1"/>
       <c r="K43" s="15"/>
     </row>
-    <row r="44" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C44" s="15"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -6820,7 +6775,7 @@
       <c r="J44" s="1"/>
       <c r="K44" s="15"/>
     </row>
-    <row r="45" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="15"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -6831,7 +6786,7 @@
       <c r="J45" s="1"/>
       <c r="K45" s="15"/>
     </row>
-    <row r="46" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="15"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -6842,7 +6797,7 @@
       <c r="J46" s="1"/>
       <c r="K46" s="15"/>
     </row>
-    <row r="47" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="15"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -6853,7 +6808,7 @@
       <c r="J47" s="1"/>
       <c r="K47" s="15"/>
     </row>
-    <row r="48" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="15"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -6864,7 +6819,7 @@
       <c r="J48" s="1"/>
       <c r="K48" s="15"/>
     </row>
-    <row r="49" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C49" s="15"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -6875,7 +6830,7 @@
       <c r="J49" s="1"/>
       <c r="K49" s="15"/>
     </row>
-    <row r="50" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="15"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -6886,7 +6841,7 @@
       <c r="J50" s="1"/>
       <c r="K50" s="15"/>
     </row>
-    <row r="51" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="15"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -6897,7 +6852,7 @@
       <c r="J51" s="1"/>
       <c r="K51" s="15"/>
     </row>
-    <row r="52" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="15"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -6908,7 +6863,7 @@
       <c r="J52" s="1"/>
       <c r="K52" s="15"/>
     </row>
-    <row r="53" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="15"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -6919,7 +6874,7 @@
       <c r="J53" s="1"/>
       <c r="K53" s="15"/>
     </row>
-    <row r="54" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="15"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -6930,7 +6885,7 @@
       <c r="J54" s="1"/>
       <c r="K54" s="15"/>
     </row>
-    <row r="55" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C55" s="15"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -6941,7 +6896,7 @@
       <c r="J55" s="1"/>
       <c r="K55" s="15"/>
     </row>
-    <row r="56" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C56" s="15"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -6952,7 +6907,7 @@
       <c r="J56" s="1"/>
       <c r="K56" s="15"/>
     </row>
-    <row r="57" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C57" s="15"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -6963,7 +6918,7 @@
       <c r="J57" s="1"/>
       <c r="K57" s="15"/>
     </row>
-    <row r="58" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C58" s="15"/>
       <c r="D58" s="1"/>
       <c r="E58" s="22"/>
@@ -6974,7 +6929,7 @@
       <c r="J58" s="15"/>
       <c r="K58" s="15"/>
     </row>
-    <row r="59" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C59" s="15"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -6985,7 +6940,7 @@
       <c r="J59" s="1"/>
       <c r="K59" s="15"/>
     </row>
-    <row r="60" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="15"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -6996,7 +6951,7 @@
       <c r="J60" s="1"/>
       <c r="K60" s="15"/>
     </row>
-    <row r="61" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="15"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -7007,7 +6962,7 @@
       <c r="J61" s="1"/>
       <c r="K61" s="15"/>
     </row>
-    <row r="62" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="15"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -7018,7 +6973,7 @@
       <c r="J62" s="1"/>
       <c r="K62" s="15"/>
     </row>
-    <row r="63" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="15"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -7029,7 +6984,7 @@
       <c r="J63" s="1"/>
       <c r="K63" s="15"/>
     </row>
-    <row r="64" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C64" s="15"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -7040,7 +6995,7 @@
       <c r="J64" s="1"/>
       <c r="K64" s="15"/>
     </row>
-    <row r="65" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="15"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -7051,7 +7006,7 @@
       <c r="J65" s="1"/>
       <c r="K65" s="15"/>
     </row>
-    <row r="66" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="15"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -7062,7 +7017,7 @@
       <c r="J66" s="1"/>
       <c r="K66" s="15"/>
     </row>
-    <row r="67" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="15"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -7073,7 +7028,7 @@
       <c r="J67" s="1"/>
       <c r="K67" s="15"/>
     </row>
-    <row r="68" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="15"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -7084,7 +7039,7 @@
       <c r="J68" s="1"/>
       <c r="K68" s="15"/>
     </row>
-    <row r="69" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="15"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -7095,7 +7050,7 @@
       <c r="J69" s="1"/>
       <c r="K69" s="15"/>
     </row>
-    <row r="70" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="15"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -7106,7 +7061,7 @@
       <c r="J70" s="1"/>
       <c r="K70" s="15"/>
     </row>
-    <row r="71" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="15"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -7117,7 +7072,7 @@
       <c r="J71" s="1"/>
       <c r="K71" s="15"/>
     </row>
-    <row r="72" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="15"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -7128,7 +7083,7 @@
       <c r="J72" s="1"/>
       <c r="K72" s="15"/>
     </row>
-    <row r="73" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="15"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -7139,7 +7094,7 @@
       <c r="J73" s="1"/>
       <c r="K73" s="15"/>
     </row>
-    <row r="74" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C74" s="15"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -7150,7 +7105,7 @@
       <c r="J74" s="1"/>
       <c r="K74" s="15"/>
     </row>
-    <row r="75" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="15"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -7161,7 +7116,7 @@
       <c r="J75" s="1"/>
       <c r="K75" s="15"/>
     </row>
-    <row r="76" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C76" s="15"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
@@ -7172,7 +7127,7 @@
       <c r="J76" s="1"/>
       <c r="K76" s="15"/>
     </row>
-    <row r="77" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C77" s="15"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -7183,7 +7138,7 @@
       <c r="J77" s="1"/>
       <c r="K77" s="15"/>
     </row>
-    <row r="78" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C78" s="15"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -7194,7 +7149,7 @@
       <c r="J78" s="1"/>
       <c r="K78" s="15"/>
     </row>
-    <row r="79" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C79" s="15"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
@@ -7205,7 +7160,7 @@
       <c r="J79" s="1"/>
       <c r="K79" s="15"/>
     </row>
-    <row r="80" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C80" s="15"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -7216,7 +7171,7 @@
       <c r="J80" s="1"/>
       <c r="K80" s="15"/>
     </row>
-    <row r="81" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C81" s="15"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
@@ -7227,7 +7182,7 @@
       <c r="J81" s="1"/>
       <c r="K81" s="15"/>
     </row>
-    <row r="82" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C82" s="15"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -7238,7 +7193,7 @@
       <c r="J82" s="1"/>
       <c r="K82" s="15"/>
     </row>
-    <row r="83" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C83" s="15"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -7249,7 +7204,7 @@
       <c r="J83" s="1"/>
       <c r="K83" s="15"/>
     </row>
-    <row r="84" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C84" s="15"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -7260,7 +7215,7 @@
       <c r="J84" s="1"/>
       <c r="K84" s="15"/>
     </row>
-    <row r="85" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C85" s="15"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -7271,7 +7226,7 @@
       <c r="J85" s="1"/>
       <c r="K85" s="15"/>
     </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C86" s="15"/>
       <c r="D86" s="15"/>
       <c r="E86" s="15"/>
@@ -7282,7 +7237,7 @@
       <c r="J86" s="15"/>
       <c r="K86" s="15"/>
     </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C87" s="15"/>
       <c r="D87" s="15"/>
       <c r="E87" s="15"/>
@@ -7304,7 +7259,7 @@
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:I363"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -7324,10 +7279,10 @@
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -7340,13 +7295,13 @@
       <c r="H3" s="11"/>
       <c r="I3" s="11"/>
     </row>
-    <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -7355,14 +7310,14 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="62" t="s">
         <v>85</v>
       </c>
@@ -7371,7 +7326,7 @@
       <c r="G7" s="64"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
@@ -7380,7 +7335,7 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="43" t="str">
         <f>HYPERLINK("#'Input - Refrigerants'!A1", "Refrigerants")</f>
         <v>Refrigerants</v>
@@ -7401,7 +7356,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="77" t="s">
         <v>93</v>
       </c>
@@ -7418,7 +7373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="77" t="s">
         <v>144</v>
       </c>
@@ -7435,7 +7390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
@@ -7455,7 +7410,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'9.1.1.1-2 Refrigerant use'!A1", "9.1.1.1-2 Refrigerant use")</f>
         <v>9.1.1.1-2 Refrigerant use</v>
@@ -7476,7 +7431,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="77" t="s">
         <v>146</v>
       </c>
@@ -7493,14 +7448,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="77"/>
       <c r="E15" s="75"/>
       <c r="F15" s="75"/>
       <c r="G15" s="76"/>
       <c r="H15" s="76"/>
     </row>
-    <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78" t="s">
         <v>1</v>
       </c>
@@ -7510,7 +7465,7 @@
       <c r="G16" s="76"/>
       <c r="H16" s="76"/>
     </row>
-    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="str">
         <f>HYPERLINK("#'Constants - Refrigerants'!A1", "Constants - Refrigerants")</f>
         <v>Constants - Refrigerants</v>
@@ -7521,7 +7476,7 @@
       <c r="G17" s="76"/>
       <c r="H17" s="76"/>
     </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -7532,40 +7487,40 @@
       <c r="G18" s="76"/>
       <c r="H18" s="76"/>
     </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="77"/>
       <c r="E19" s="75"/>
       <c r="F19" s="75"/>
       <c r="G19" s="76"/>
       <c r="H19" s="76"/>
     </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="48"/>
       <c r="I38" s="48"/>
     </row>
-    <row r="39" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="48"/>
       <c r="I39" s="48"/>
     </row>
-    <row r="40" spans="1:9" s="49" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" s="49" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -7575,7 +7530,7 @@
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
-    <row r="41" spans="1:9" s="49" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" s="49" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -7585,131 +7540,131 @@
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
-    <row r="42" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" spans="4:4" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D363" s="38"/>
     </row>
   </sheetData>
@@ -7813,7 +7768,7 @@
     <tabColor rgb="FF008000"/>
   </sheetPr>
   <dimension ref="A1:M342"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -7831,10 +7786,10 @@
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -7853,13 +7808,13 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
     </row>
-    <row r="4" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -7869,7 +7824,7 @@
         <v>The total emissions of refrigerant leaking during operation (not during installation or disposal)</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="4" t="str" cm="1">
         <f t="array" ref="D6">Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeaking_Source()</f>
         <v>VEERG 2026: 9.1.1, Equation (1)</v>
@@ -7883,7 +7838,7 @@
       <c r="K6" s="66"/>
       <c r="L6" s="66"/>
     </row>
-    <row r="7" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="29" t="str" cm="1">
         <f t="array" ref="D7">Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeaking_Variation()</f>
         <v>VARIATION ON SOURCE: Added equation to convert refrigerant R to CO2-e using the refrigerant's global warming potential (GWP).</v>
@@ -7896,7 +7851,7 @@
       <c r="K7" s="66"/>
       <c r="L7" s="66"/>
     </row>
-    <row r="8" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
@@ -7915,7 +7870,7 @@
       <c r="K8" s="66"/>
       <c r="L8" s="66"/>
     </row>
-    <row r="9" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - Refrigerants'!A1", "Refrigerants")</f>
         <v>Refrigerants</v>
@@ -7927,7 +7882,7 @@
       <c r="K9" s="66"/>
       <c r="L9" s="66"/>
     </row>
-    <row r="10" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G10" s="66"/>
       <c r="H10" s="66"/>
       <c r="I10" s="66"/>
@@ -7935,7 +7890,7 @@
       <c r="K10" s="66"/>
       <c r="L10" s="66"/>
     </row>
-    <row r="11" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
@@ -7950,7 +7905,7 @@
       <c r="K11" s="66"/>
       <c r="L11" s="66"/>
     </row>
-    <row r="12" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
@@ -7969,7 +7924,7 @@
       <c r="K12" s="66"/>
       <c r="L12" s="66"/>
     </row>
-    <row r="13" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="60" t="str">
         <f>HYPERLINK("#'9.1.1.1-2 Refrigerant use'!A1", "9.1.1.1-2 Refrigerant use")</f>
         <v>9.1.1.1-2 Refrigerant use</v>
@@ -7984,7 +7939,7 @@
       <c r="K13" s="66"/>
       <c r="L13" s="66"/>
     </row>
-    <row r="14" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="51" t="str" cm="1">
         <f t="array" ref="D14:E17">_xlfn.CHOOSECOLS(Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeaking_Arguments(), 1, 2)</f>
         <v>charge_Ra</v>
@@ -8005,7 +7960,7 @@
       <c r="K14" s="66"/>
       <c r="L14" s="66"/>
     </row>
-    <row r="15" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="51" t="str">
         <v>leakagerate_a</v>
       </c>
@@ -8024,7 +7979,7 @@
       <c r="K15" s="66"/>
       <c r="L15" s="66"/>
     </row>
-    <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78" t="s">
         <v>1</v>
       </c>
@@ -8046,7 +8001,7 @@
       <c r="K16" s="66"/>
       <c r="L16" s="66"/>
     </row>
-    <row r="17" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="str">
         <f>HYPERLINK("#'Constants - Refrigerants'!A1", "Constants - Refrigerants")</f>
         <v>Constants - Refrigerants</v>
@@ -8069,7 +8024,7 @@
       <c r="K17" s="66"/>
       <c r="L17" s="66"/>
     </row>
-    <row r="18" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -8081,7 +8036,7 @@
       <c r="K18" s="66"/>
       <c r="L18" s="66"/>
     </row>
-    <row r="19" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="66" t="s">
         <v>139</v>
       </c>
@@ -8094,12 +8049,12 @@
       <c r="K19" s="66"/>
       <c r="L19" s="66"/>
     </row>
-    <row r="20" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="35" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="26" t="s">
         <v>88</v>
       </c>
@@ -8128,7 +8083,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="27" t="str" cm="1">
         <f t="array" ref="D22:D31">IFERROR(INDEX(Table_Input_Refrigerant[Refrigeration unit name], _xlfn.SEQUENCE(10)),"")</f>
         <v>Cool room</v>
@@ -8166,7 +8121,7 @@
         <v>8.5000000000000006E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="27" t="str">
         <v>Office air con units</v>
       </c>
@@ -8199,7 +8154,7 @@
         <v>1.7500000000000003E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="27" t="str">
         <v>Car AC</v>
       </c>
@@ -8232,7 +8187,7 @@
         <v>8.7100000000000007E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="27" t="str">
         <v>Storage AC</v>
       </c>
@@ -8265,7 +8220,7 @@
         <v>3.5000000000000005E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="27" t="str">
         <v>Refrigerated trucks</v>
       </c>
@@ -8298,7 +8253,7 @@
         <v>1.5699999999999999E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="27">
         <v>0</v>
       </c>
@@ -8331,7 +8286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="27">
         <v>0</v>
       </c>
@@ -8364,7 +8319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="27">
         <v>0</v>
       </c>
@@ -8397,7 +8352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="27">
         <v>0</v>
       </c>
@@ -8430,7 +8385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="27">
         <v>0</v>
       </c>
@@ -8463,18 +8418,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="36" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="34" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="35" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="35" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="26" t="s">
         <v>129</v>
       </c>
@@ -8482,7 +8437,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="36" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="27" t="str" cm="1">
         <f t="array" ref="D36:D39">_xlfn.UNIQUE(_xlfn._xlws.FILTER(F22:F31, (F22:F31&lt;&gt;"") * (F22:F31&lt;&gt;0)))</f>
         <v>R-402A</v>
@@ -8496,7 +8451,7 @@
       <c r="K36" s="66"/>
       <c r="L36" s="66"/>
     </row>
-    <row r="37" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="27" t="str">
         <v>R-422B</v>
       </c>
@@ -8509,7 +8464,7 @@
       <c r="K37" s="66"/>
       <c r="L37" s="66"/>
     </row>
-    <row r="38" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="27" t="str">
         <v>R-400 60/40</v>
       </c>
@@ -8522,7 +8477,7 @@
       <c r="K38" s="66"/>
       <c r="L38" s="66"/>
     </row>
-    <row r="39" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="27" t="str">
         <v>R-504</v>
       </c>
@@ -8533,7 +8488,7 @@
       <c r="H39" s="66"/>
       <c r="I39" s="66"/>
     </row>
-    <row r="40" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="27"/>
       <c r="E40" s="27">
         <f>SUMIF($F$22:$F$31,VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend5_Name_Method1,$L$22:$L$31)</f>
@@ -8542,7 +8497,7 @@
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
     </row>
-    <row r="41" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="27"/>
       <c r="E41" s="27">
         <f>SUMIF($F$22:$F$31,VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend6_Name_Method1,$L$22:$L$31)</f>
@@ -8551,7 +8506,7 @@
       <c r="H41" s="66"/>
       <c r="I41" s="66"/>
     </row>
-    <row r="42" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="27"/>
       <c r="E42" s="27">
         <f>SUMIF($F$22:$F$31,VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend7_Name_Method1,$L$22:$L$31)</f>
@@ -8560,7 +8515,7 @@
       <c r="H42" s="66"/>
       <c r="I42" s="66"/>
     </row>
-    <row r="43" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="27"/>
       <c r="E43" s="27">
         <f>SUMIF($F$22:$F$31,VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend8_Name_Method1,$L$22:$L$31)</f>
@@ -8569,7 +8524,7 @@
       <c r="H43" s="66"/>
       <c r="I43" s="66"/>
     </row>
-    <row r="44" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="27"/>
       <c r="E44" s="27">
         <f>SUMIF($F$22:$F$31,VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend9_Name_Method1,$L$22:$L$31)</f>
@@ -8578,7 +8533,7 @@
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
     </row>
-    <row r="45" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="27"/>
       <c r="E45" s="27">
         <f>SUMIF($F$22:$F$31,VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend10_Name_Method1,$L$22:$L$31)</f>
@@ -8587,9 +8542,9 @@
       <c r="H45" s="66"/>
       <c r="I45" s="66"/>
     </row>
-    <row r="46" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="69"/>
       <c r="D48" s="69"/>
       <c r="E48" s="69"/>
@@ -8602,13 +8557,13 @@
       <c r="L48" s="69"/>
       <c r="M48" s="69"/>
     </row>
-    <row r="49" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="5" t="str" cm="1">
         <f t="array" ref="D49">Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeakingGWP_Title()</f>
         <v>Refrigerant leakage emissions converted to CO2-e</v>
       </c>
     </row>
-    <row r="50" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="10" t="s">
         <v>9</v>
       </c>
@@ -8617,9 +8572,9 @@
         <v>=Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeakingGWP</v>
       </c>
     </row>
-    <row r="51" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="2" t="s">
         <v>12</v>
       </c>
@@ -8628,7 +8583,7 @@
         <v>E_CO2e</v>
       </c>
     </row>
-    <row r="54" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="2" t="s">
         <v>4</v>
       </c>
@@ -8637,8 +8592,8 @@
         <v>t CO2-e</v>
       </c>
     </row>
-    <row r="55" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="51" t="str" cm="1">
         <f t="array" ref="D56:E57">_xlfn.CHOOSECOLS(Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeakingGWP_Arguments(), 1,2)</f>
         <v>E_R</v>
@@ -8659,7 +8614,7 @@
         <v>Table_E_R</v>
       </c>
     </row>
-    <row r="57" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="51" t="str">
         <v>GWP_R</v>
       </c>
@@ -8678,18 +8633,18 @@
         <v>Table_E_CO2e</v>
       </c>
     </row>
-    <row r="58" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="36" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="60" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D60" s="35" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="61" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="26" t="s">
         <v>129</v>
       </c>
@@ -8703,7 +8658,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="62" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D62" s="27" t="str">
         <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend1_Name_Method1</f>
         <v>R-402A</v>
@@ -8721,7 +8676,7 @@
         <v>1.1860424000000003</v>
       </c>
     </row>
-    <row r="63" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="27" t="str">
         <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend2_Name_Method1</f>
         <v>R-422B</v>
@@ -8739,7 +8694,7 @@
         <v>2.0794287500000004</v>
       </c>
     </row>
-    <row r="64" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="27" t="str">
         <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend3_Name_Method1</f>
         <v>R-400 60/40</v>
@@ -8757,7 +8712,7 @@
         <v>70.007256000000027</v>
       </c>
     </row>
-    <row r="65" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="27" t="str">
         <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend4_Name_Method1</f>
         <v>R-504</v>
@@ -8775,7 +8730,7 @@
         <v>34.780656319599998</v>
       </c>
     </row>
-    <row r="66" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="27">
         <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend5_Name_Method1</f>
         <v>0</v>
@@ -8793,7 +8748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D67" s="27">
         <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend6_Name_Method1</f>
         <v>0</v>
@@ -8811,7 +8766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D68" s="27">
         <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend7_Name_Method1</f>
         <v>0</v>
@@ -8829,7 +8784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="27">
         <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend8_Name_Method1</f>
         <v>0</v>
@@ -8847,7 +8802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="27">
         <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend9_Name_Method1</f>
         <v>0</v>
@@ -8865,7 +8820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="27">
         <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend10_Name_Method1</f>
         <v>0</v>
@@ -8883,8 +8838,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D73" s="72" t="s">
         <v>137</v>
       </c>
@@ -8897,208 +8852,208 @@
         <v>t CO2-e</v>
       </c>
     </row>
-    <row r="74" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="8:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="H341" s="15"/>
     </row>
-    <row r="342" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="8:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="H342" s="15"/>
     </row>
   </sheetData>
@@ -9117,7 +9072,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:AI180"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -9144,13 +9099,13 @@
       <c r="AH1"/>
       <c r="AI1"/>
     </row>
-    <row r="2" spans="1:35" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
       <c r="AG2"/>
       <c r="AH2"/>
       <c r="AI2"/>
     </row>
-    <row r="3" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -9186,13 +9141,13 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -9212,7 +9167,7 @@
       <c r="P5" s="66"/>
       <c r="Q5" s="66"/>
     </row>
-    <row r="6" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="4" t="str" cm="1">
         <f t="array" ref="D6">Refrigerants_SourceData.Refrigerants_ChemicalGWP_Source()</f>
         <v>Australian National Greenhouse Accounts Factors 2025 - Appendix 2 - Table 23</v>
@@ -9231,7 +9186,7 @@
       <c r="P6" s="66"/>
       <c r="Q6" s="66"/>
     </row>
-    <row r="7" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="29" t="str" cm="1">
         <f t="array" ref="D7">"⚠️" &amp; Refrigerants_SourceData.Refrigerants_ChemicalGWP_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added 'GAS - FC name' column with truncated gas name to allow matching with other tables. Added extra gases from IPCC Global Warming Potential Values v2.0 - (AR5). Added 'Additional data source' column.</v>
@@ -9247,7 +9202,7 @@
       <c r="P7" s="66"/>
       <c r="Q7" s="66"/>
     </row>
-    <row r="8" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
@@ -9276,7 +9231,7 @@
       <c r="P8" s="66"/>
       <c r="Q8" s="66"/>
     </row>
-    <row r="9" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - Refrigerants'!A1", "Refrigerants")</f>
         <v>Refrigerants</v>
@@ -9311,7 +9266,7 @@
       <c r="P9" s="66"/>
       <c r="Q9" s="66"/>
     </row>
-    <row r="10" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="24" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>Methane</v>
@@ -9342,7 +9297,7 @@
       <c r="P10" s="66"/>
       <c r="Q10" s="66"/>
     </row>
-    <row r="11" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="24" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>Nitrous oxide</v>
@@ -9373,7 +9328,7 @@
       <c r="P11" s="66"/>
       <c r="Q11" s="66"/>
     </row>
-    <row r="12" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
@@ -9407,7 +9362,7 @@
       <c r="P12" s="66"/>
       <c r="Q12" s="66"/>
     </row>
-    <row r="13" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'9.1.1.1-2 Refrigerant use'!A1", "9.1.1.1-2 Refrigerant use")</f>
         <v>9.1.1.1-2 Refrigerant use</v>
@@ -9442,7 +9397,7 @@
       <c r="P13" s="66"/>
       <c r="Q13" s="66"/>
     </row>
-    <row r="14" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="24" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HFC-32 (R-32)</v>
@@ -9473,7 +9428,7 @@
       <c r="P14" s="66"/>
       <c r="Q14" s="66"/>
     </row>
-    <row r="15" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="24" t="str" cm="1">
         <f t="array" ref="D15">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HFC-41 (R-41)</v>
@@ -9504,7 +9459,7 @@
       <c r="P15" s="66"/>
       <c r="Q15" s="66"/>
     </row>
-    <row r="16" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78" t="s">
         <v>1</v>
       </c>
@@ -9538,7 +9493,7 @@
       <c r="P16" s="66"/>
       <c r="Q16" s="66"/>
     </row>
-    <row r="17" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="61" t="str">
         <f>HYPERLINK("#'Constants - Refrigerants'!A1", "Constants - Refrigerants")</f>
         <v>Constants - Refrigerants</v>
@@ -9573,7 +9528,7 @@
       <c r="P17" s="66"/>
       <c r="Q17" s="66"/>
     </row>
-    <row r="18" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -9608,7 +9563,7 @@
       <c r="P18" s="66"/>
       <c r="Q18" s="66"/>
     </row>
-    <row r="19" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="24" t="str" cm="1">
         <f t="array" ref="D19">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HFC-134a (R-134a)</v>
@@ -9639,7 +9594,7 @@
       <c r="P19" s="66"/>
       <c r="Q19" s="66"/>
     </row>
-    <row r="20" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="24" t="str" cm="1">
         <f t="array" ref="D20">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HFC-143 (R-143)</v>
@@ -9670,7 +9625,7 @@
       <c r="P20" s="66"/>
       <c r="Q20" s="66"/>
     </row>
-    <row r="21" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="24" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HFC-143a (R-143a)</v>
@@ -9701,7 +9656,7 @@
       <c r="P21" s="66"/>
       <c r="Q21" s="66"/>
     </row>
-    <row r="22" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="24" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HFC-152a (R-152a)</v>
@@ -9732,7 +9687,7 @@
       <c r="P22" s="66"/>
       <c r="Q22" s="66"/>
     </row>
-    <row r="23" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="24" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HFC-227ea (R-227ea)</v>
@@ -9763,7 +9718,7 @@
       <c r="P23" s="66"/>
       <c r="Q23" s="66"/>
     </row>
-    <row r="24" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="24" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HFC-236fa (R-236fa)</v>
@@ -9794,7 +9749,7 @@
       <c r="P24" s="66"/>
       <c r="Q24" s="66"/>
     </row>
-    <row r="25" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="24" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HFC-245ca (R-245ca)</v>
@@ -9825,7 +9780,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="24" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HFC-245fa (R-245fa)</v>
@@ -9856,7 +9811,7 @@
       <c r="P26" s="66"/>
       <c r="Q26" s="66"/>
     </row>
-    <row r="27" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="24" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HFC-365mfc (R-365mfc)</v>
@@ -9887,7 +9842,7 @@
       <c r="P27" s="66"/>
       <c r="Q27" s="66"/>
     </row>
-    <row r="28" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="24" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HCFC-22 (R-22)</v>
@@ -9918,7 +9873,7 @@
       <c r="P28" s="66"/>
       <c r="Q28" s="66"/>
     </row>
-    <row r="29" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="68" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HCFC-123 (R-123)</v>
@@ -9949,7 +9904,7 @@
       <c r="P29" s="66"/>
       <c r="Q29" s="66"/>
     </row>
-    <row r="30" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="68" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HCFC-124 (R-124)</v>
@@ -9980,7 +9935,7 @@
       <c r="P30" s="66"/>
       <c r="Q30" s="66"/>
     </row>
-    <row r="31" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="68" t="str" cm="1">
         <f t="array" ref="D31">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HCFC-141b (R-141b)</v>
@@ -10011,7 +9966,7 @@
       <c r="P31" s="66"/>
       <c r="Q31" s="66"/>
     </row>
-    <row r="32" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="68" t="str" cm="1">
         <f t="array" ref="D32">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HCFC-142b (R-142b)</v>
@@ -10042,7 +9997,7 @@
       <c r="P32" s="66"/>
       <c r="Q32" s="66"/>
     </row>
-    <row r="33" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="68" t="str" cm="1">
         <f t="array" ref="D33">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HCFC-225ca (R-225ca)</v>
@@ -10073,7 +10028,7 @@
       <c r="P33" s="66"/>
       <c r="Q33" s="66"/>
     </row>
-    <row r="34" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="68" t="str" cm="1">
         <f t="array" ref="D34">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>HCFC-225cb (R-225cb)</v>
@@ -10104,7 +10059,7 @@
       <c r="P34" s="66"/>
       <c r="Q34" s="66"/>
     </row>
-    <row r="35" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="68" t="str" cm="1">
         <f t="array" ref="D35">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>PFC-14 Perfluoromethane (tetrafluoromethane)</v>
@@ -10135,7 +10090,7 @@
       <c r="P35" s="66"/>
       <c r="Q35" s="66"/>
     </row>
-    <row r="36" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="68" t="str" cm="1">
         <f t="array" ref="D36">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>PFC-116 Perfluoroethane (hexafluoroethane)</v>
@@ -10166,7 +10121,7 @@
       <c r="P36" s="66"/>
       <c r="Q36" s="66"/>
     </row>
-    <row r="37" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="68" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>PFC-218 Perfluoropropane</v>
@@ -10197,7 +10152,7 @@
       <c r="P37" s="66"/>
       <c r="Q37" s="66"/>
     </row>
-    <row r="38" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="68" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>PFC-31-10 Perfluorobutane</v>
@@ -10228,7 +10183,7 @@
       <c r="P38" s="66"/>
       <c r="Q38" s="66"/>
     </row>
-    <row r="39" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="68" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>PFC-318 Perfluorocyclobutane</v>
@@ -10259,7 +10214,7 @@
       <c r="P39" s="66"/>
       <c r="Q39" s="66"/>
     </row>
-    <row r="40" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="68" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>PFC-41-12 Perfluoropentane</v>
@@ -10290,7 +10245,7 @@
       <c r="P40" s="66"/>
       <c r="Q40" s="66"/>
     </row>
-    <row r="41" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="68" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>PFC-51-14 Perfluorohexane</v>
@@ -10321,7 +10276,7 @@
       <c r="P41" s="66"/>
       <c r="Q41" s="66"/>
     </row>
-    <row r="42" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="68" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>PFC-91-18 Perflunafene</v>
@@ -10352,7 +10307,7 @@
       <c r="P42" s="66"/>
       <c r="Q42" s="66"/>
     </row>
-    <row r="43" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="68" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>CFC-12</v>
@@ -10383,7 +10338,7 @@
       <c r="P43" s="66"/>
       <c r="Q43" s="66"/>
     </row>
-    <row r="44" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="68" t="str" cm="1">
         <f t="array" ref="D44">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>CFC-13</v>
@@ -10414,7 +10369,7 @@
       <c r="P44" s="66"/>
       <c r="Q44" s="66"/>
     </row>
-    <row r="45" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="68" t="str" cm="1">
         <f t="array" ref="D45">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>CFC-114</v>
@@ -10445,7 +10400,7 @@
       <c r="P45" s="66"/>
       <c r="Q45" s="66"/>
     </row>
-    <row r="46" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="68" t="str" cm="1">
         <f t="array" ref="D46">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalGWP_Data(), Table_RefrigerantChemicalGWP[[#Headers],[Gas]], 0)</f>
         <v>CFC-115</v>
@@ -10476,7 +10431,7 @@
       <c r="P46" s="66"/>
       <c r="Q46" s="66"/>
     </row>
-    <row r="47" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="66"/>
       <c r="E47" s="66"/>
       <c r="F47" s="66"/>
@@ -10492,7 +10447,7 @@
       <c r="P47" s="66"/>
       <c r="Q47" s="66"/>
     </row>
-    <row r="48" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="69"/>
       <c r="E48" s="69"/>
       <c r="F48" s="69"/>
@@ -10508,7 +10463,7 @@
       <c r="P48" s="70"/>
       <c r="Q48" s="70"/>
     </row>
-    <row r="49" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="5" t="str" cm="1">
         <f t="array" ref="D49">Refrigerants_SourceData.Refrigerants_ChemicalBlends_Title()</f>
         <v>Blended refrigerants (many containing HFCS and/or PFCS)</v>
@@ -10524,7 +10479,7 @@
       <c r="P49" s="66"/>
       <c r="Q49" s="66"/>
     </row>
-    <row r="50" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="4" t="str" cm="1">
         <f t="array" ref="D50">Refrigerants_SourceData.Refrigerants_ChemicalBlends_Source()</f>
         <v>Australian National Greenhouse Accounts Factors 2025 - Appendix 2 - Table 24</v>
@@ -10543,7 +10498,7 @@
       <c r="P50" s="66"/>
       <c r="Q50" s="66"/>
     </row>
-    <row r="51" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="29" t="str" cm="1">
         <f t="array" ref="D51">"⚠️" &amp; Refrigerants_SourceData.Refrigerants_ChemicalBlends_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Fixed typo - changed HC600a to HC-600a for blend R-414B. Fixed typo for blend R-405A - Changed HCFC142b to HCFC-142b.</v>
@@ -10559,7 +10514,7 @@
       <c r="P51" s="66"/>
       <c r="Q51" s="66"/>
     </row>
-    <row r="52" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D52" s="68" t="s">
         <v>104</v>
       </c>
@@ -10581,7 +10536,7 @@
       <c r="P52" s="66"/>
       <c r="Q52" s="66"/>
     </row>
-    <row r="53" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="68" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-400</v>
@@ -10606,7 +10561,7 @@
       <c r="P53" s="66"/>
       <c r="Q53" s="66"/>
     </row>
-    <row r="54" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="68" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-401A</v>
@@ -10631,7 +10586,7 @@
       <c r="P54" s="66"/>
       <c r="Q54" s="66"/>
     </row>
-    <row r="55" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="68" t="str" cm="1">
         <f t="array" ref="D55">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-401B</v>
@@ -10656,7 +10611,7 @@
       <c r="P55" s="66"/>
       <c r="Q55" s="66"/>
     </row>
-    <row r="56" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="68" t="str" cm="1">
         <f t="array" ref="D56">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-401C</v>
@@ -10681,7 +10636,7 @@
       <c r="P56" s="66"/>
       <c r="Q56" s="66"/>
     </row>
-    <row r="57" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="68" t="str" cm="1">
         <f t="array" ref="D57">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-402A</v>
@@ -10706,7 +10661,7 @@
       <c r="P57" s="66"/>
       <c r="Q57" s="66"/>
     </row>
-    <row r="58" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D58" s="68" t="str" cm="1">
         <f t="array" ref="D58">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-402B</v>
@@ -10731,7 +10686,7 @@
       <c r="P58" s="66"/>
       <c r="Q58" s="66"/>
     </row>
-    <row r="59" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="68" t="str" cm="1">
         <f t="array" ref="D59">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-403A</v>
@@ -10756,7 +10711,7 @@
       <c r="P59" s="66"/>
       <c r="Q59" s="66"/>
     </row>
-    <row r="60" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D60" s="68" t="str" cm="1">
         <f t="array" ref="D60">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-403B</v>
@@ -10781,7 +10736,7 @@
       <c r="P60" s="66"/>
       <c r="Q60" s="66"/>
     </row>
-    <row r="61" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="68" t="str" cm="1">
         <f t="array" ref="D61">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-404A</v>
@@ -10806,7 +10761,7 @@
       <c r="P61" s="66"/>
       <c r="Q61" s="66"/>
     </row>
-    <row r="62" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D62" s="68" t="str" cm="1">
         <f t="array" ref="D62">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-405A</v>
@@ -10831,7 +10786,7 @@
       <c r="P62" s="66"/>
       <c r="Q62" s="66"/>
     </row>
-    <row r="63" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="68" t="str" cm="1">
         <f t="array" ref="D63">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-406A</v>
@@ -10856,7 +10811,7 @@
       <c r="P63" s="66"/>
       <c r="Q63" s="66"/>
     </row>
-    <row r="64" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="68" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-407A</v>
@@ -10881,7 +10836,7 @@
       <c r="P64" s="66"/>
       <c r="Q64" s="66"/>
     </row>
-    <row r="65" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="68" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-407B</v>
@@ -10906,7 +10861,7 @@
       <c r="P65" s="66"/>
       <c r="Q65" s="66"/>
     </row>
-    <row r="66" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="68" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-407C</v>
@@ -10931,7 +10886,7 @@
       <c r="P66" s="66"/>
       <c r="Q66" s="66"/>
     </row>
-    <row r="67" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D67" s="68" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-407D</v>
@@ -10956,7 +10911,7 @@
       <c r="P67" s="66"/>
       <c r="Q67" s="66"/>
     </row>
-    <row r="68" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D68" s="68" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-407E</v>
@@ -10981,7 +10936,7 @@
       <c r="P68" s="66"/>
       <c r="Q68" s="66"/>
     </row>
-    <row r="69" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="68" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-408A</v>
@@ -11006,7 +10961,7 @@
       <c r="P69" s="66"/>
       <c r="Q69" s="66"/>
     </row>
-    <row r="70" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="68" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-409A</v>
@@ -11031,7 +10986,7 @@
       <c r="P70" s="66"/>
       <c r="Q70" s="66"/>
     </row>
-    <row r="71" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="68" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-409B</v>
@@ -11056,7 +11011,7 @@
       <c r="P71" s="66"/>
       <c r="Q71" s="66"/>
     </row>
-    <row r="72" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D72" s="68" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-410A</v>
@@ -11081,7 +11036,7 @@
       <c r="P72" s="66"/>
       <c r="Q72" s="66"/>
     </row>
-    <row r="73" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D73" s="68" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-410B</v>
@@ -11106,7 +11061,7 @@
       <c r="P73" s="66"/>
       <c r="Q73" s="66"/>
     </row>
-    <row r="74" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D74" s="68" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-411A</v>
@@ -11131,7 +11086,7 @@
       <c r="P74" s="66"/>
       <c r="Q74" s="66"/>
     </row>
-    <row r="75" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D75" s="68" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-411B</v>
@@ -11156,7 +11111,7 @@
       <c r="P75" s="66"/>
       <c r="Q75" s="66"/>
     </row>
-    <row r="76" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D76" s="68" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-411C</v>
@@ -11181,7 +11136,7 @@
       <c r="P76" s="66"/>
       <c r="Q76" s="66"/>
     </row>
-    <row r="77" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D77" s="68" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-412A</v>
@@ -11206,7 +11161,7 @@
       <c r="P77" s="66"/>
       <c r="Q77" s="66"/>
     </row>
-    <row r="78" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D78" s="68" t="str" cm="1">
         <f t="array" ref="D78">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-413A</v>
@@ -11231,7 +11186,7 @@
       <c r="P78" s="66"/>
       <c r="Q78" s="66"/>
     </row>
-    <row r="79" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D79" s="68" t="str" cm="1">
         <f t="array" ref="D79">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-414A</v>
@@ -11256,7 +11211,7 @@
       <c r="P79" s="66"/>
       <c r="Q79" s="66"/>
     </row>
-    <row r="80" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D80" s="68" t="str" cm="1">
         <f t="array" ref="D80">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-414B</v>
@@ -11281,7 +11236,7 @@
       <c r="P80" s="66"/>
       <c r="Q80" s="66"/>
     </row>
-    <row r="81" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="68" t="str" cm="1">
         <f t="array" ref="D81">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-415A</v>
@@ -11306,7 +11261,7 @@
       <c r="P81" s="66"/>
       <c r="Q81" s="66"/>
     </row>
-    <row r="82" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D82" s="68" t="str" cm="1">
         <f t="array" ref="D82">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-415B</v>
@@ -11331,7 +11286,7 @@
       <c r="P82" s="66"/>
       <c r="Q82" s="66"/>
     </row>
-    <row r="83" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D83" s="68" t="str" cm="1">
         <f t="array" ref="D83">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-416A</v>
@@ -11356,7 +11311,7 @@
       <c r="P83" s="66"/>
       <c r="Q83" s="66"/>
     </row>
-    <row r="84" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D84" s="68" t="str" cm="1">
         <f t="array" ref="D84">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-417A</v>
@@ -11381,7 +11336,7 @@
       <c r="P84" s="66"/>
       <c r="Q84" s="66"/>
     </row>
-    <row r="85" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D85" s="68" t="str" cm="1">
         <f t="array" ref="D85">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-418A</v>
@@ -11406,7 +11361,7 @@
       <c r="P85" s="66"/>
       <c r="Q85" s="66"/>
     </row>
-    <row r="86" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D86" s="68" t="str" cm="1">
         <f t="array" ref="D86">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-419A</v>
@@ -11431,7 +11386,7 @@
       <c r="P86" s="66"/>
       <c r="Q86" s="66"/>
     </row>
-    <row r="87" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D87" s="68" t="str" cm="1">
         <f t="array" ref="D87">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-420A</v>
@@ -11456,7 +11411,7 @@
       <c r="P87" s="66"/>
       <c r="Q87" s="66"/>
     </row>
-    <row r="88" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D88" s="68" t="str" cm="1">
         <f t="array" ref="D88">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-421A</v>
@@ -11481,7 +11436,7 @@
       <c r="P88" s="66"/>
       <c r="Q88" s="66"/>
     </row>
-    <row r="89" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D89" s="68" t="str" cm="1">
         <f t="array" ref="D89">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-422A</v>
@@ -11506,7 +11461,7 @@
       <c r="P89" s="66"/>
       <c r="Q89" s="66"/>
     </row>
-    <row r="90" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D90" s="68" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-422B</v>
@@ -11531,7 +11486,7 @@
       <c r="P90" s="66"/>
       <c r="Q90" s="66"/>
     </row>
-    <row r="91" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D91" s="68" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-422C</v>
@@ -11556,7 +11511,7 @@
       <c r="P91" s="66"/>
       <c r="Q91" s="66"/>
     </row>
-    <row r="92" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D92" s="68" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-500</v>
@@ -11581,7 +11536,7 @@
       <c r="P92" s="66"/>
       <c r="Q92" s="66"/>
     </row>
-    <row r="93" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D93" s="68" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-501</v>
@@ -11606,7 +11561,7 @@
       <c r="P93" s="66"/>
       <c r="Q93" s="66"/>
     </row>
-    <row r="94" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D94" s="68" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-502</v>
@@ -11631,7 +11586,7 @@
       <c r="P94" s="66"/>
       <c r="Q94" s="66"/>
     </row>
-    <row r="95" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D95" s="68" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-503</v>
@@ -11656,7 +11611,7 @@
       <c r="P95" s="66"/>
       <c r="Q95" s="66"/>
     </row>
-    <row r="96" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D96" s="68" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-504</v>
@@ -11681,7 +11636,7 @@
       <c r="P96" s="66"/>
       <c r="Q96" s="66"/>
     </row>
-    <row r="97" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D97" s="68" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-505</v>
@@ -11706,7 +11661,7 @@
       <c r="P97" s="66"/>
       <c r="Q97" s="66"/>
     </row>
-    <row r="98" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D98" s="68" t="str" cm="1">
         <f t="array" ref="D98">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-506</v>
@@ -11731,7 +11686,7 @@
       <c r="P98" s="66"/>
       <c r="Q98" s="66"/>
     </row>
-    <row r="99" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D99" s="68" t="str" cm="1">
         <f t="array" ref="D99">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-507A</v>
@@ -11756,7 +11711,7 @@
       <c r="P99" s="66"/>
       <c r="Q99" s="66"/>
     </row>
-    <row r="100" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="68" t="str" cm="1">
         <f t="array" ref="D100">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-508A</v>
@@ -11781,7 +11736,7 @@
       <c r="P100" s="66"/>
       <c r="Q100" s="66"/>
     </row>
-    <row r="101" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D101" s="68" t="str" cm="1">
         <f t="array" ref="D101">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-508B</v>
@@ -11806,7 +11761,7 @@
       <c r="P101" s="66"/>
       <c r="Q101" s="66"/>
     </row>
-    <row r="102" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D102" s="68" t="str" cm="1">
         <f t="array" ref="D102">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_ChemicalBlends_Data(), Table_RefrigerantBlends[[#Headers],[Blend]], 0)</f>
         <v>R-509A</v>
@@ -11831,7 +11786,7 @@
       <c r="P102" s="66"/>
       <c r="Q102" s="66"/>
     </row>
-    <row r="103" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D103" s="66"/>
       <c r="E103" s="66"/>
       <c r="F103" s="66"/>
@@ -11847,7 +11802,7 @@
       <c r="P103" s="66"/>
       <c r="Q103" s="66"/>
     </row>
-    <row r="104" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D104" s="70"/>
       <c r="E104" s="70"/>
       <c r="F104" s="70"/>
@@ -11863,7 +11818,7 @@
       <c r="P104" s="70"/>
       <c r="Q104" s="70"/>
     </row>
-    <row r="105" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="5" t="s">
         <v>107</v>
       </c>
@@ -11881,7 +11836,7 @@
       <c r="P105" s="66"/>
       <c r="Q105" s="66"/>
     </row>
-    <row r="106" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D106" s="62" t="str">
         <f>"  ℹ️  This table lists the refrigerant blends from the table '"&amp;D49&amp;"' and each constituent gas in separate cells. For each constituent gas, it GWP value is found from the '"&amp;D5&amp;"' table. Then the GWPs for each constituent gas are miltiplied by their blend fraction, and added together to make a GWP for the blend."</f>
         <v xml:space="preserve">  ℹ️  This table lists the refrigerant blends from the table 'Blended refrigerants (many containing HFCS and/or PFCS)' and each constituent gas in separate cells. For each constituent gas, it GWP value is found from the 'Global Warming Potentials' table. Then the GWPs for each constituent gas are miltiplied by their blend fraction, and added together to make a GWP for the blend.</v>
@@ -11900,7 +11855,7 @@
       <c r="P106" s="66"/>
       <c r="Q106" s="66"/>
     </row>
-    <row r="107" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D107" s="29" t="str">
         <f>"⚠️NOTE: Some constituent gases are not listed in the '" &amp; D5 &amp; "' table. This is because those gases are not reportable under AR5."</f>
         <v>⚠️NOTE: Some constituent gases are not listed in the 'Global Warming Potentials' table. This is because those gases are not reportable under AR5.</v>
@@ -11919,7 +11874,7 @@
       <c r="P107" s="66"/>
       <c r="Q107" s="66"/>
     </row>
-    <row r="108" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D108" s="29" t="str">
         <f>"⚠️NOTE: Because there are no specified blends of R-400 in the table '" &amp; D49 &amp; "' We have specified three blends: 'R-400 50/50', 'R-400 60/40' and 'R-400 80/20'"</f>
         <v>⚠️NOTE: Because there are no specified blends of R-400 in the table 'Blended refrigerants (many containing HFCS and/or PFCS)' We have specified three blends: 'R-400 50/50', 'R-400 60/40' and 'R-400 80/20'</v>
@@ -11938,7 +11893,7 @@
       <c r="P108" s="66"/>
       <c r="Q108" s="66"/>
     </row>
-    <row r="109" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D109" s="68" t="s">
         <v>104</v>
       </c>
@@ -11982,7 +11937,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="110" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D110" s="68" t="str">
         <f>$D$53 &amp; " 50/50"</f>
         <v>R-400 50/50</v>
@@ -12032,7 +11987,7 @@
         <v>4697.5</v>
       </c>
     </row>
-    <row r="111" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D111" s="68" t="str">
         <f>$D$53 &amp; " 60/40"</f>
         <v>R-400 60/40</v>
@@ -12082,7 +12037,7 @@
         <v>5733.6</v>
       </c>
     </row>
-    <row r="112" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D112" s="68" t="str">
         <f>$D$53 &amp; " 80/20"</f>
         <v>R-400 80/20</v>
@@ -12132,7 +12087,7 @@
         <v>7902.4</v>
       </c>
     </row>
-    <row r="113" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D113" s="68" t="str">
         <f t="shared" ref="D113:D161" si="0">D54</f>
         <v>R-401A</v>
@@ -12190,7 +12145,7 @@
         <v>557.63740000000007</v>
       </c>
     </row>
-    <row r="114" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D114" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-401B</v>
@@ -12248,7 +12203,7 @@
         <v>697.88260000000002</v>
       </c>
     </row>
-    <row r="115" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D115" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-401C</v>
@@ -12306,7 +12261,7 @@
         <v>337.26980000000003</v>
       </c>
     </row>
-    <row r="116" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D116" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-402A</v>
@@ -12364,7 +12319,7 @@
         <v>1395.3440000000001</v>
       </c>
     </row>
-    <row r="117" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D117" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-402B</v>
@@ -12422,7 +12377,7 @@
         <v>1091.348</v>
       </c>
     </row>
-    <row r="118" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D118" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-403A</v>
@@ -12480,7 +12435,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="119" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D119" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-403B</v>
@@ -12538,7 +12493,7 @@
         <v>1905.6260000000002</v>
       </c>
     </row>
-    <row r="120" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D120" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-404A</v>
@@ -12596,7 +12551,7 @@
         <v>1913.712</v>
       </c>
     </row>
-    <row r="121" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D121" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-405A</v>
@@ -12654,7 +12609,7 @@
         <v>2086.2282</v>
       </c>
     </row>
-    <row r="122" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D122" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-406A</v>
@@ -12712,7 +12667,7 @@
         <v>865.23800000000017</v>
       </c>
     </row>
-    <row r="123" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D123" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-407A</v>
@@ -12770,7 +12725,7 @@
         <v>742.28000000000009</v>
       </c>
     </row>
-    <row r="124" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D124" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-407B</v>
@@ -12828,7 +12783,7 @@
         <v>1612.0700000000002</v>
       </c>
     </row>
-    <row r="125" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D125" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-407C</v>
@@ -12886,7 +12841,7 @@
         <v>585.45830000000001</v>
       </c>
     </row>
-    <row r="126" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D126" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-407D</v>
@@ -12944,7 +12899,7 @@
         <v>723.55750000000012</v>
       </c>
     </row>
-    <row r="127" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D127" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-407E</v>
@@ -13002,7 +12957,7 @@
         <v>581.63750000000005</v>
       </c>
     </row>
-    <row r="128" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D128" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-408A</v>
@@ -13060,7 +13015,7 @@
         <v>1419.9970000000001</v>
       </c>
     </row>
-    <row r="129" spans="4:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:33" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D129" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-409A</v>
@@ -13118,7 +13073,7 @@
         <v>711.08749999999998</v>
       </c>
     </row>
-    <row r="130" spans="4:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:33" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D130" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-409B</v>
@@ -13177,7 +13132,7 @@
       </c>
       <c r="AG130" s="1"/>
     </row>
-    <row r="131" spans="4:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="4:33" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D131" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-410A</v>
@@ -13236,7 +13191,7 @@
       </c>
       <c r="AG131" s="1"/>
     </row>
-    <row r="132" spans="4:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="4:33" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D132" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-410B</v>
@@ -13295,7 +13250,7 @@
       </c>
       <c r="AG132" s="1"/>
     </row>
-    <row r="133" spans="4:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:33" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D133" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-411A</v>
@@ -13354,7 +13309,7 @@
       </c>
       <c r="AG133" s="1"/>
     </row>
-    <row r="134" spans="4:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:33" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D134" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-411B</v>
@@ -13413,7 +13368,7 @@
       </c>
       <c r="AG134" s="1"/>
     </row>
-    <row r="135" spans="4:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:33" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D135" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-411C</v>
@@ -13472,7 +13427,7 @@
       </c>
       <c r="AG135" s="1"/>
     </row>
-    <row r="136" spans="4:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:33" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D136" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-412A</v>
@@ -13531,7 +13486,7 @@
       </c>
       <c r="AG136" s="1"/>
     </row>
-    <row r="137" spans="4:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="4:33" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D137" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-413A</v>
@@ -13590,7 +13545,7 @@
       </c>
       <c r="AG137" s="1"/>
     </row>
-    <row r="138" spans="4:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="4:33" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D138" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-414A</v>
@@ -13649,7 +13604,7 @@
       </c>
       <c r="AG138" s="1"/>
     </row>
-    <row r="139" spans="4:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="4:33" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D139" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-414B</v>
@@ -13708,7 +13663,7 @@
       </c>
       <c r="AG139" s="1"/>
     </row>
-    <row r="140" spans="4:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="4:33" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D140" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-415A</v>
@@ -13766,7 +13721,7 @@
         <v>1187.8952000000002</v>
       </c>
     </row>
-    <row r="141" spans="4:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="4:33" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D141" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-415B</v>
@@ -13824,7 +13779,7 @@
         <v>187.625</v>
       </c>
     </row>
-    <row r="142" spans="4:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="4:33" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D142" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-416A</v>
@@ -13882,7 +13837,7 @@
         <v>534.75517500000001</v>
       </c>
     </row>
-    <row r="143" spans="4:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="4:33" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D143" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-417A</v>
@@ -13940,7 +13895,7 @@
         <v>1013.3845200000001</v>
       </c>
     </row>
-    <row r="144" spans="4:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="4:33" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D144" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-418A</v>
@@ -13998,7 +13953,7 @@
         <v>1622.1022499999999</v>
       </c>
     </row>
-    <row r="145" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D145" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-419A</v>
@@ -14056,7 +14011,7 @@
         <v>1926.4230000000002</v>
       </c>
     </row>
-    <row r="146" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D146" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-420A</v>
@@ -14114,7 +14069,7 @@
         <v>1035.232</v>
       </c>
     </row>
-    <row r="147" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D147" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-421A</v>
@@ -14172,7 +14127,7 @@
         <v>1295.7079999999999</v>
       </c>
     </row>
-    <row r="148" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D148" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-422A</v>
@@ -14230,7 +14185,7 @@
         <v>2312.90967</v>
       </c>
     </row>
-    <row r="149" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D149" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-422B</v>
@@ -14288,7 +14243,7 @@
         <v>1188.2450000000001</v>
       </c>
     </row>
-    <row r="150" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D150" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-422C</v>
@@ -14346,7 +14301,7 @@
         <v>2160.7580000000003</v>
       </c>
     </row>
-    <row r="151" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D151" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-500</v>
@@ -14404,7 +14359,7 @@
         <v>5564.8416719999996</v>
       </c>
     </row>
-    <row r="152" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D152" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-501</v>
@@ -14462,7 +14417,7 @@
         <v>1627.5</v>
       </c>
     </row>
-    <row r="153" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D153" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-502</v>
@@ -14520,7 +14475,7 @@
         <v>2429.77792</v>
       </c>
     </row>
-    <row r="154" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D154" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-503</v>
@@ -14578,7 +14533,7 @@
         <v>6981.2663000000002</v>
       </c>
     </row>
-    <row r="155" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D155" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-504</v>
@@ -14636,7 +14591,7 @@
         <v>2215.3284279999998</v>
       </c>
     </row>
-    <row r="156" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D156" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-505</v>
@@ -14694,7 +14649,7 @@
         <v>6205.68</v>
       </c>
     </row>
-    <row r="157" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D157" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-506</v>
@@ -14752,7 +14707,7 @@
         <v>1731.7525900000003</v>
       </c>
     </row>
-    <row r="158" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D158" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-507A</v>
@@ -14810,7 +14765,7 @@
         <v>1992.5</v>
       </c>
     </row>
-    <row r="159" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D159" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-508A</v>
@@ -14868,7 +14823,7 @@
         <v>6016.3499999999995</v>
       </c>
     </row>
-    <row r="160" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D160" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-508B</v>
@@ -14926,7 +14881,7 @@
         <v>5860.6</v>
       </c>
     </row>
-    <row r="161" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="68" t="str">
         <f t="shared" si="0"/>
         <v>R-509A</v>
@@ -14984,7 +14939,7 @@
         <v>3131.7760000000007</v>
       </c>
     </row>
-    <row r="162" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="66"/>
       <c r="E162" s="66"/>
       <c r="F162" s="66"/>
@@ -15000,7 +14955,7 @@
       <c r="P162" s="66"/>
       <c r="Q162" s="66"/>
     </row>
-    <row r="163" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="70"/>
       <c r="E163" s="70"/>
       <c r="F163" s="70"/>
@@ -15016,7 +14971,7 @@
       <c r="P163" s="70"/>
       <c r="Q163" s="70"/>
     </row>
-    <row r="164" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="5" t="str" cm="1">
         <f t="array" ref="D164">Refrigerants_SourceData.Refrigerants_LeakageRates_Title()</f>
         <v>Indicative leakage rates for common refrigeration and air - conditioning equipment</v>
@@ -15035,7 +14990,7 @@
       <c r="P164" s="66"/>
       <c r="Q164" s="66"/>
     </row>
-    <row r="165" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D165" s="4" t="str" cm="1">
         <f t="array" ref="D165">Refrigerants_SourceData.Refrigerants_LeakageRates_Source()</f>
         <v>Australian National Greenhouse Accounts Factors 2025 - Table 10</v>
@@ -15054,7 +15009,7 @@
       <c r="P165" s="66"/>
       <c r="Q165" s="66"/>
     </row>
-    <row r="166" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:17" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D166" s="66"/>
       <c r="E166" s="66"/>
       <c r="F166" s="66"/>
@@ -15070,7 +15025,7 @@
       <c r="P166" s="66"/>
       <c r="Q166" s="66"/>
     </row>
-    <row r="167" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:17" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D167" s="68" t="s">
         <v>121</v>
       </c>
@@ -15090,7 +15045,7 @@
       <c r="P167" s="66"/>
       <c r="Q167" s="66"/>
     </row>
-    <row r="168" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:17" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D168" s="68" t="str" cm="1">
         <f t="array" ref="D168">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_LeakageRates_Data(), Table_Refrigerants_LeakageRates[[#Headers],[Product]], 0)</f>
         <v>Domestic refrigerators</v>
@@ -15112,7 +15067,7 @@
       <c r="P168" s="66"/>
       <c r="Q168" s="66"/>
     </row>
-    <row r="169" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:17" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D169" s="68" t="str" cm="1">
         <f t="array" ref="D169">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_LeakageRates_Data(), Table_Refrigerants_LeakageRates[[#Headers],[Product]], 0)</f>
         <v>Transport refrigeration</v>
@@ -15134,7 +15089,7 @@
       <c r="P169" s="66"/>
       <c r="Q169" s="66"/>
     </row>
-    <row r="170" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:17" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D170" s="68" t="str" cm="1">
         <f t="array" ref="D170">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_LeakageRates_Data(), Table_Refrigerants_LeakageRates[[#Headers],[Product]], 0)</f>
         <v>Domestic A/C portable</v>
@@ -15156,7 +15111,7 @@
       <c r="P170" s="66"/>
       <c r="Q170" s="66"/>
     </row>
-    <row r="171" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:17" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D171" s="68" t="str" cm="1">
         <f t="array" ref="D171">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_LeakageRates_Data(), Table_Refrigerants_LeakageRates[[#Headers],[Product]], 0)</f>
         <v>Domestic A/C split</v>
@@ -15178,7 +15133,7 @@
       <c r="P171" s="66"/>
       <c r="Q171" s="66"/>
     </row>
-    <row r="172" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:17" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D172" s="68" t="str" cm="1">
         <f t="array" ref="D172">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_LeakageRates_Data(), Table_Refrigerants_LeakageRates[[#Headers],[Product]], 0)</f>
         <v>Domestic A/C packaged</v>
@@ -15200,7 +15155,7 @@
       <c r="P172" s="66"/>
       <c r="Q172" s="66"/>
     </row>
-    <row r="173" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:17" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D173" s="68" t="str" cm="1">
         <f t="array" ref="D173">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_LeakageRates_Data(), Table_Refrigerants_LeakageRates[[#Headers],[Product]], 0)</f>
         <v>Light vehicle A/C</v>
@@ -15222,7 +15177,7 @@
       <c r="P173" s="66"/>
       <c r="Q173" s="66"/>
     </row>
-    <row r="174" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:17" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D174" s="68" t="str" cm="1">
         <f t="array" ref="D174">Common_InputFunctions.Utility_DisplayArrayInTable(Refrigerants_SourceData.Refrigerants_LeakageRates_Data(), Table_Refrigerants_LeakageRates[[#Headers],[Product]], 0)</f>
         <v>Heavy vehicle A/C</v>
@@ -15244,7 +15199,7 @@
       <c r="P174" s="66"/>
       <c r="Q174" s="66"/>
     </row>
-    <row r="175" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:17" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D175" s="66"/>
       <c r="E175" s="66"/>
       <c r="F175" s="66"/>
@@ -15260,7 +15215,7 @@
       <c r="P175" s="66"/>
       <c r="Q175" s="66"/>
     </row>
-    <row r="176" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:17" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D176" s="66"/>
       <c r="E176" s="66"/>
       <c r="F176" s="66"/>
@@ -15276,7 +15231,7 @@
       <c r="P176" s="66"/>
       <c r="Q176" s="66"/>
     </row>
-    <row r="177" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:17" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D177" s="66"/>
       <c r="E177" s="66"/>
       <c r="F177" s="66"/>
@@ -15292,7 +15247,7 @@
       <c r="P177" s="66"/>
       <c r="Q177" s="66"/>
     </row>
-    <row r="178" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:17" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D178" s="66"/>
       <c r="E178" s="66"/>
       <c r="F178" s="66"/>
@@ -15308,7 +15263,7 @@
       <c r="P178" s="66"/>
       <c r="Q178" s="66"/>
     </row>
-    <row r="179" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:17" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D179" s="66"/>
       <c r="E179" s="66"/>
       <c r="F179" s="66"/>
@@ -15324,7 +15279,7 @@
       <c r="P179" s="66"/>
       <c r="Q179" s="66"/>
     </row>
-    <row r="180" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:17" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D180" s="66"/>
       <c r="E180" s="66"/>
       <c r="F180" s="66"/>
@@ -15358,7 +15313,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:BY297"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="6" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="6" customWidth="1"/>
@@ -15391,10 +15346,10 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -15421,11 +15376,11 @@
       <c r="V3" s="9"/>
       <c r="W3" s="9"/>
     </row>
-    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="BM4" s="2"/>
     </row>
-    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="D5" s="5" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
@@ -15433,7 +15388,7 @@
       </c>
       <c r="BM5" s="2"/>
     </row>
-    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="78" t="s">
         <v>1</v>
       </c>
@@ -15447,7 +15402,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="61" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -15465,7 +15420,7 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -15483,7 +15438,7 @@
         <v>ACT</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="D9" s="24" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -15498,7 +15453,7 @@
         <v>VIC</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="D10" s="24" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -15513,7 +15468,7 @@
         <v>QLD</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="D11" s="24" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -15529,7 +15484,7 @@
       </c>
       <c r="BM11" s="2"/>
     </row>
-    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="24" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -15545,7 +15500,7 @@
       </c>
       <c r="BM12" s="2"/>
     </row>
-    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="D13" s="24" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -15560,7 +15515,7 @@
         <v>TAS</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="D14" s="24" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -15575,129 +15530,129 @@
         <v>NT</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="D18" s="5" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="D19" s="4" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="D20" s="24" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="24" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="24" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="D23" s="24" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="D24" s="24" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="D25" s="24" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="D26" s="24" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="D27" s="24" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="D28" s="24" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="D29" s="24" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="D30" s="24" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="D34" s="5" t="str" cm="1">
         <f t="array" ref="D34">Common_SourceData.Common_SourceData_GWP_Title()</f>
         <v>Global warming potential for greenhouse gases</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="D35" s="4" t="str" cm="1">
         <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="24" t="s">
         <v>10</v>
@@ -15706,7 +15661,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="24" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -15717,7 +15672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="24" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -15728,7 +15683,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="24" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -15739,7 +15694,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="24" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -15750,7 +15705,7 @@
         <v>6630</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="D41" s="24" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -15761,7 +15716,7 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="D42" s="24" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -15772,7 +15727,7 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="D43" s="24" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -15783,24 +15738,24 @@
         <v>17200</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="D45" s="5" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="D46" s="4" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="D47" s="24" t="s">
         <v>10</v>
@@ -15818,7 +15773,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="D48" s="24" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -15841,7 +15796,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="D49" s="24" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -15864,7 +15819,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="D50" s="24" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -15887,7 +15842,7 @@
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="D51" s="24" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -15910,7 +15865,7 @@
         <v>3.2857142857142856</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="D52" s="24" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -15933,7 +15888,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
       <c r="D53" s="24" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -15956,7 +15911,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="D54" s="24" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -15979,49 +15934,49 @@
         <v>1.1666666666666667</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="D57" s="5" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="D58" s="4" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="D59" s="29" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="D60" s="29" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="D61" s="29" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="D63" s="24" t="s">
         <v>3</v>
@@ -16030,7 +15985,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="D64" s="24" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -16041,7 +15996,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="D65" s="24" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -16052,7 +16007,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="D66" s="24" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -16063,7 +16018,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="D67" s="24" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -16074,7 +16029,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="D68" s="24" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -16085,7 +16040,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="D69" s="24" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -16096,7 +16051,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="D70" s="24" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -16107,7 +16062,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="D71" s="24" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -16118,7 +16073,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="D72" s="24" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -16129,7 +16084,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="D73" s="24" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -16140,7 +16095,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
       <c r="D74" s="24" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -16151,7 +16106,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
       <c r="D75" s="24" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -16162,7 +16117,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="D76" s="24" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -16173,7 +16128,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="D77" s="24" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -16184,64 +16139,64 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="D81" s="5" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="D82" s="4" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
       <c r="D83" s="29" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="D84" s="29" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="D85" s="29" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="D86" s="29" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="D87" s="29" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="D89" s="24" t="s">
         <v>3</v>
@@ -16293,7 +16248,7 @@
       </c>
       <c r="T89" s="24"/>
     </row>
-    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="D90" s="24" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -16361,7 +16316,7 @@
       </c>
       <c r="T90" s="24"/>
     </row>
-    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="D91" s="24" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -16429,7 +16384,7 @@
       </c>
       <c r="T91" s="24"/>
     </row>
-    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="D92" s="24" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -16497,7 +16452,7 @@
       </c>
       <c r="T92" s="24"/>
     </row>
-    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="D93" s="24" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -16565,7 +16520,7 @@
       </c>
       <c r="T93" s="24"/>
     </row>
-    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="D94" s="24" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -16633,7 +16588,7 @@
       </c>
       <c r="T94" s="24"/>
     </row>
-    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="D95" s="24" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -16701,7 +16656,7 @@
       </c>
       <c r="T95" s="24"/>
     </row>
-    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="D96" s="24" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -16769,7 +16724,7 @@
       </c>
       <c r="T96" s="24"/>
     </row>
-    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="D97" s="24" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -16837,66 +16792,66 @@
       </c>
       <c r="T97" s="24"/>
     </row>
-    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="D99" s="28" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="D100" s="28" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="D101" s="28" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
       <c r="D102" s="28" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="D103" s="28"/>
     </row>
-    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
       <c r="D105" s="5" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
       <c r="D106" s="4" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
       <c r="D107" s="29" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109"/>
       <c r="D109" s="24" t="s">
         <v>35</v>
@@ -16911,7 +16866,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110"/>
       <c r="D110" s="24" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -16930,7 +16885,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111"/>
       <c r="D111" s="24" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -16949,7 +16904,7 @@
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112"/>
       <c r="D112" s="24" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -16968,13 +16923,13 @@
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115"/>
       <c r="D115" s="5" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
@@ -16982,7 +16937,7 @@
       </c>
       <c r="BN115" s="6"/>
     </row>
-    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116"/>
       <c r="D116" s="4" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
@@ -16990,7 +16945,7 @@
       </c>
       <c r="BN116" s="6"/>
     </row>
-    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117"/>
       <c r="D117" s="29" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
@@ -16998,11 +16953,11 @@
       </c>
       <c r="BN117" s="6"/>
     </row>
-    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118"/>
       <c r="BN118" s="6"/>
     </row>
-    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119"/>
       <c r="D119" s="24" t="s">
         <v>38</v>
@@ -17018,7 +16973,7 @@
       </c>
       <c r="BN119" s="6"/>
     </row>
-    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120"/>
       <c r="D120" s="24" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -17038,7 +16993,7 @@
       </c>
       <c r="BN120" s="6"/>
     </row>
-    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121"/>
       <c r="D121" s="24" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -17058,31 +17013,31 @@
       </c>
       <c r="BN121" s="6"/>
     </row>
-    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122"/>
       <c r="BN122" s="6"/>
     </row>
-    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124"/>
       <c r="D124" s="5" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125"/>
       <c r="D125" s="4" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127"/>
       <c r="D127" s="24" t="s">
         <v>40</v>
@@ -17091,7 +17046,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128"/>
       <c r="D128" s="24" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -17102,7 +17057,7 @@
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129"/>
       <c r="D129" s="24" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -17113,13 +17068,13 @@
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132"/>
       <c r="D132" s="5" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
@@ -17127,7 +17082,7 @@
       </c>
       <c r="E132" s="15"/>
     </row>
-    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133"/>
       <c r="D133" s="4" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
@@ -17135,7 +17090,7 @@
       </c>
       <c r="E133" s="15"/>
     </row>
-    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134"/>
       <c r="D134" t="s">
         <v>46</v>
@@ -17144,7 +17099,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135"/>
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -17155,7 +17110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136"/>
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -17166,10 +17121,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138"/>
       <c r="BN138" s="6"/>
       <c r="BO138" s="6"/>
@@ -17184,7 +17139,7 @@
       <c r="BX138" s="6"/>
       <c r="BY138" s="6"/>
     </row>
-    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139"/>
       <c r="D139" s="5" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
@@ -17203,7 +17158,7 @@
       <c r="BX139" s="6"/>
       <c r="BY139" s="6"/>
     </row>
-    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140"/>
       <c r="D140" s="4" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
@@ -17222,7 +17177,7 @@
       <c r="BX140" s="6"/>
       <c r="BY140" s="6"/>
     </row>
-    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141"/>
       <c r="D141" s="29" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
@@ -17230,7 +17185,7 @@
       </c>
       <c r="BN141" s="6"/>
     </row>
-    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142"/>
       <c r="D142" s="24" t="s">
         <v>57</v>
@@ -17240,7 +17195,7 @@
       </c>
       <c r="BN142" s="6"/>
     </row>
-    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143"/>
       <c r="D143" s="24" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -17252,7 +17207,7 @@
       </c>
       <c r="BN143" s="6"/>
     </row>
-    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144"/>
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -17264,7 +17219,7 @@
       </c>
       <c r="BN144" s="6"/>
     </row>
-    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145"/>
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -17276,7 +17231,7 @@
       </c>
       <c r="BN145" s="6"/>
     </row>
-    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146"/>
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -17288,7 +17243,7 @@
       </c>
       <c r="BN146" s="6"/>
     </row>
-    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147"/>
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -17300,15 +17255,15 @@
       </c>
       <c r="BN147" s="6"/>
     </row>
-    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148"/>
       <c r="BN148" s="6"/>
     </row>
-    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149"/>
       <c r="BN149" s="6"/>
     </row>
-    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150"/>
       <c r="D150" s="5" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
@@ -17316,7 +17271,7 @@
       </c>
       <c r="BN150" s="6"/>
     </row>
-    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151"/>
       <c r="D151" s="4" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
@@ -17324,11 +17279,11 @@
       </c>
       <c r="BN151" s="6"/>
     </row>
-    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152"/>
       <c r="BN152" s="6"/>
     </row>
-    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153"/>
       <c r="D153" s="24" t="s">
         <v>42</v>
@@ -17348,7 +17303,7 @@
       <c r="BL153" s="2"/>
       <c r="BM153" s="2"/>
     </row>
-    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154"/>
       <c r="D154" s="24" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -17370,7 +17325,7 @@
       <c r="BL154" s="2"/>
       <c r="BM154" s="2"/>
     </row>
-    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155"/>
       <c r="D155" s="24" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -17392,7 +17347,7 @@
       <c r="BL155" s="2"/>
       <c r="BM155" s="2"/>
     </row>
-    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156"/>
       <c r="D156" s="24" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -17403,7 +17358,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157"/>
       <c r="D157" s="24" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -17414,7 +17369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158"/>
       <c r="D158" s="24" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -17425,34 +17380,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160"/>
     </row>
-    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="5" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="15"/>
     </row>
-    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="4" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="15"/>
     </row>
-    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="4" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="15"/>
     </row>
-    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="15" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -17461,17 +17416,17 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN165" s="6"/>
       <c r="BO165" s="6"/>
       <c r="BP165" s="6"/>
     </row>
-    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN166" s="6"/>
       <c r="BO166" s="6"/>
       <c r="BP166" s="6"/>
     </row>
-    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="5" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
@@ -17480,7 +17435,7 @@
       <c r="BO167" s="6"/>
       <c r="BP167" s="6"/>
     </row>
-    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="4" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
@@ -17489,7 +17444,7 @@
       <c r="BO168" s="6"/>
       <c r="BP168" s="6"/>
     </row>
-    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="4" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
@@ -17498,7 +17453,7 @@
       <c r="BO169" s="6"/>
       <c r="BP169" s="6"/>
     </row>
-    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -17510,17 +17465,17 @@
       <c r="BO170" s="6"/>
       <c r="BP170" s="6"/>
     </row>
-    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN171" s="6"/>
       <c r="BO171" s="6"/>
       <c r="BP171" s="6"/>
     </row>
-    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN172" s="6"/>
       <c r="BO172" s="6"/>
       <c r="BP172" s="6"/>
     </row>
-    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="5" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
@@ -17529,7 +17484,7 @@
       <c r="BO173" s="6"/>
       <c r="BP173" s="6"/>
     </row>
-    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="4" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
@@ -17538,7 +17493,7 @@
       <c r="BO174" s="6"/>
       <c r="BP174" s="6"/>
     </row>
-    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -17551,17 +17506,17 @@
       <c r="BO175" s="6"/>
       <c r="BP175" s="6"/>
     </row>
-    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN176" s="6"/>
       <c r="BO176" s="6"/>
       <c r="BP176" s="6"/>
     </row>
-    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN177" s="6"/>
       <c r="BO177" s="6"/>
       <c r="BP177" s="6"/>
     </row>
-    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="5" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
@@ -17570,7 +17525,7 @@
       <c r="BO178" s="6"/>
       <c r="BP178" s="6"/>
     </row>
-    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="4" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
@@ -17579,39 +17534,39 @@
       <c r="BO179" s="6"/>
       <c r="BP179" s="6"/>
     </row>
-    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="28" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="29" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="29" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="29" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="29" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="29" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="24" t="s">
         <v>50</v>
       </c>
@@ -17628,7 +17583,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="24" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
@@ -17650,7 +17605,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="24" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
@@ -17672,7 +17627,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="24" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -17694,7 +17649,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="24" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -17716,7 +17671,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="24" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
@@ -17738,7 +17693,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="24" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
@@ -17760,7 +17715,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="24" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
@@ -17782,7 +17737,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="24" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
@@ -17804,7 +17759,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="24" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
@@ -17826,7 +17781,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="24" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
@@ -17848,7 +17803,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D197" s="24" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
@@ -17870,7 +17825,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D198" s="24" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
@@ -17892,7 +17847,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D199" s="24" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
@@ -17914,31 +17869,31 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D202" s="5" t="str" cm="1">
         <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
         <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
       </c>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D203" s="4" t="str" cm="1">
         <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
         <v>VEERG 2026: Table A.2.2.2</v>
       </c>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D204" s="29" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D205" s="28" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D206" s="24" t="s">
         <v>3</v>
       </c>
@@ -17946,7 +17901,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D207" s="24" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -17956,7 +17911,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D208" s="1" t="str" cm="1">
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -17966,13 +17921,13 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D211" s="1" t="str" cm="1">
         <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
         <v>Months to Seasons Mapping</v>
       </c>
     </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D212" s="24" t="s">
         <v>56</v>
       </c>
@@ -17980,7 +17935,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D213" s="24" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
@@ -17990,7 +17945,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D214" s="1" t="str" cm="1">
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
@@ -18000,7 +17955,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D215" s="1" t="str" cm="1">
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
@@ -18010,7 +17965,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D216" s="1" t="str" cm="1">
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
@@ -18020,7 +17975,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D217" s="1" t="str" cm="1">
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
@@ -18030,7 +17985,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D218" s="1" t="str" cm="1">
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
@@ -18040,7 +17995,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D219" s="1" t="str" cm="1">
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
@@ -18050,7 +18005,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D220" s="1" t="str" cm="1">
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
@@ -18060,7 +18015,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D221" s="1" t="str" cm="1">
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
@@ -18070,7 +18025,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D222" s="1" t="str" cm="1">
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
@@ -18080,7 +18035,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D223" s="1" t="str" cm="1">
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
@@ -18090,7 +18045,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D224" s="1" t="str" cm="1">
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
@@ -18100,25 +18055,25 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D227" s="5" t="str" cm="1">
         <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
         <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
       </c>
     </row>
-    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D228" s="4" t="str" cm="1">
         <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
         <v>VEERG 2026: Table A.1.8.1</v>
       </c>
     </row>
-    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D229" s="29" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
-    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D231" s="24" t="s">
         <v>34</v>
       </c>
@@ -18168,7 +18123,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D232" s="24" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -18234,7 +18189,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D233" s="1" t="str" cm="1">
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -18300,7 +18255,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D234" s="1" t="str" cm="1">
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -18366,7 +18321,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D235" s="1" t="str" cm="1">
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -18432,7 +18387,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D236" s="1" t="str" cm="1">
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -18498,7 +18453,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D237" s="1" t="str" cm="1">
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -18564,7 +18519,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D238" s="1" t="str" cm="1">
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -18630,7 +18585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D239" s="1" t="str" cm="1">
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -18696,7 +18651,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D240" s="1" t="str" cm="1">
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -18762,7 +18717,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D241" s="1" t="str" cm="1">
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -18828,7 +18783,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D242" s="1" t="str" cm="1">
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -18894,7 +18849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D243" s="1" t="str" cm="1">
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -18960,7 +18915,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D244" s="1" t="str" cm="1">
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19026,7 +18981,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D245" s="1" t="str" cm="1">
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19092,7 +19047,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D246" s="1" t="str" cm="1">
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19158,7 +19113,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D247" s="1" t="str" cm="1">
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19224,7 +19179,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D248" s="1" t="str" cm="1">
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -19290,7 +19245,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D249" s="1" t="str" cm="1">
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -19356,7 +19311,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D250" s="1" t="str" cm="1">
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -19422,31 +19377,31 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D253" s="5" t="str" cm="1">
         <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
         <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
       </c>
     </row>
-    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D254" s="4" t="str" cm="1">
         <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
         <v>VEERG 2026: Table A.2.1.4</v>
       </c>
     </row>
-    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D255" s="1" t="str" cm="1">
         <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
         <v>EFNi &amp; EFN2Oi</v>
       </c>
     </row>
-    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D256" s="28" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D257" s="24" t="s">
         <v>78</v>
       </c>
@@ -19454,7 +19409,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="258" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D258" s="24" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -19464,7 +19419,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D259" s="1" t="str" cm="1">
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -19474,17 +19429,17 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:6" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D263" s="5" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="264" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D264" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="265" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D265" s="24" t="s">
         <v>155</v>
       </c>
@@ -19495,7 +19450,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="266" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D266" s="24" t="s">
         <v>158</v>
       </c>
@@ -19506,7 +19461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D267" s="24" t="s">
         <v>160</v>
       </c>
@@ -19517,7 +19472,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D268" s="24" t="s">
         <v>162</v>
       </c>
@@ -19528,7 +19483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D269" s="24" t="s">
         <v>164</v>
       </c>
@@ -19539,7 +19494,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D270" s="24" t="s">
         <v>166</v>
       </c>
@@ -19550,12 +19505,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D273" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="274" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D274" s="24" t="s">
         <v>155</v>
       </c>
@@ -19566,7 +19521,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="275" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D275" s="24" t="s">
         <v>169</v>
       </c>
@@ -19577,7 +19532,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D276" s="24" t="s">
         <v>171</v>
       </c>
@@ -19588,7 +19543,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D277" s="24" t="s">
         <v>173</v>
       </c>
@@ -19599,7 +19554,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="278" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D278" s="24" t="s">
         <v>175</v>
       </c>
@@ -19610,7 +19565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D279" s="24" t="s">
         <v>177</v>
       </c>
@@ -19621,12 +19576,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D282" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="283" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D283" s="24" t="s">
         <v>155</v>
       </c>
@@ -19637,7 +19592,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="284" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D284" s="24" t="s">
         <v>180</v>
       </c>
@@ -19648,7 +19603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D285" s="24" t="s">
         <v>182</v>
       </c>
@@ -19659,7 +19614,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D286" s="24" t="s">
         <v>184</v>
       </c>
@@ -19670,7 +19625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D287" s="24" t="s">
         <v>186</v>
       </c>
@@ -19681,7 +19636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D288" s="24" t="s">
         <v>188</v>
       </c>
@@ -19692,12 +19647,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D291" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="292" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D292" s="24" t="s">
         <v>155</v>
       </c>
@@ -19708,7 +19663,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="293" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D293" s="24" t="s">
         <v>191</v>
       </c>
@@ -19719,7 +19674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D294" s="24" t="s">
         <v>193</v>
       </c>
@@ -19730,7 +19685,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D295" s="24" t="s">
         <v>195</v>
       </c>
@@ -19741,7 +19696,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D296" s="24" t="s">
         <v>197</v>
       </c>
@@ -19752,7 +19707,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D297" s="24" t="s">
         <v>199</v>
       </c>
